--- a/templates/GOA_template.xlsx
+++ b/templates/GOA_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Desktop\GOA_Main\GOA_LLM\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4593C099-B7EB-40D0-9615-6F576B102044}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5630886-DC51-47FD-9CA6-B08D713D11DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-18617" yWindow="-18617" windowWidth="33120" windowHeight="18000" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2523" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2520" uniqueCount="575">
   <si>
     <t>General Order Acknowledgement - Data Entry</t>
   </si>
@@ -873,12 +873,6 @@
     <t>OBSO (checkbox)</t>
   </si>
   <si>
-    <t>Double wall â€“ Nitro &amp; Fill (checkbox)</t>
-  </si>
-  <si>
-    <t>Nozzle Body Size ~</t>
-  </si>
-  <si>
     <t>6 mm (checkbox)</t>
   </si>
   <si>
@@ -891,18 +885,6 @@
     <t>12mm (checkbox)</t>
   </si>
   <si>
-    <t>Â½" (checkbox)</t>
-  </si>
-  <si>
-    <t>â…œ (checkbox)</t>
-  </si>
-  <si>
-    <t>Â¾ (checkbox)</t>
-  </si>
-  <si>
-    <t>â€” (checkbox)</t>
-  </si>
-  <si>
     <t>Nozzle Bar / Stations</t>
   </si>
   <si>
@@ -1107,9 +1089,6 @@
     <t>Grip &amp; Dive (checkbox)</t>
   </si>
   <si>
-    <t>Belts â€“ on the fly (checkbox)</t>
-  </si>
-  <si>
     <t>AC (checkbox)</t>
   </si>
   <si>
@@ -1305,33 +1284,6 @@
     <t>Package On (checkbox)</t>
   </si>
   <si>
-    <t>2 Bottle Orientation SYS (checkbox)</t>
-  </si>
-  <si>
-    <t>8 HD P/P Servo (checkbox)</t>
-  </si>
-  <si>
-    <t>1 Mag w/12 Rows (checkbox)</t>
-  </si>
-  <si>
-    <t>Inspection</t>
-  </si>
-  <si>
-    <t>Top (checkbox)</t>
-  </si>
-  <si>
-    <t>Side (checkbox)</t>
-  </si>
-  <si>
-    <t>Corner (checkbox)</t>
-  </si>
-  <si>
-    <t>Application</t>
-  </si>
-  <si>
-    <t>Cap &amp; Body (checkbox)</t>
-  </si>
-  <si>
     <t>Enercon Model</t>
   </si>
   <si>
@@ -1464,15 +1416,6 @@
     <t>Width</t>
   </si>
   <si>
-    <t>3Â¼" (checkbox)</t>
-  </si>
-  <si>
-    <t>4Â½" (checkbox)</t>
-  </si>
-  <si>
-    <t>7Â½" (checkbox)</t>
-  </si>
-  <si>
     <t>Length O.L</t>
   </si>
   <si>
@@ -1497,9 +1440,6 @@
     <t>U (checkbox)</t>
   </si>
   <si>
-    <t>90Â° (checkbox)</t>
-  </si>
-  <si>
     <t>Chain Type</t>
   </si>
   <si>
@@ -1765,6 +1705,60 @@
   </si>
   <si>
     <t>Fixed (STD for Explosive Enviroment)(checkbox)</t>
+  </si>
+  <si>
+    <t>Yes (requires 15" HMI) (checkbox)</t>
+  </si>
+  <si>
+    <t>Clear Bottle Sensor</t>
+  </si>
+  <si>
+    <t>N/A (checkbox)</t>
+  </si>
+  <si>
+    <t>Pharma Type Software Logging</t>
+  </si>
+  <si>
+    <t>UPS (checkbox)</t>
+  </si>
+  <si>
+    <t>BeltStar System Specifications - Cap or Torque</t>
+  </si>
+  <si>
+    <t>Belts - on the fly (checkbox)</t>
+  </si>
+  <si>
+    <t>3¼" (checkbox)</t>
+  </si>
+  <si>
+    <t>4½" (checkbox)</t>
+  </si>
+  <si>
+    <t>7½" (checkbox)</t>
+  </si>
+  <si>
+    <t>90° (checkbox)</t>
+  </si>
+  <si>
+    <t>½" (checkbox)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nozzle Body Size </t>
+  </si>
+  <si>
+    <t>¼" (checkbox)</t>
+  </si>
+  <si>
+    <t>⅜" (checkbox)</t>
+  </si>
+  <si>
+    <t>⅝" (checkbox)</t>
+  </si>
+  <si>
+    <t>¾” (checkbox)</t>
+  </si>
+  <si>
+    <t>Double wall - Nitro &amp; Fill (checkbox)</t>
   </si>
 </sst>
 </file>
@@ -1909,8 +1903,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D5A367C9-9BB7-480B-A164-754BE967D3D7}" name="Table1" displayName="Table1" ref="A1:F632" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
-  <autoFilter ref="A1:F632" xr:uid="{D5A367C9-9BB7-480B-A164-754BE967D3D7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{D5A367C9-9BB7-480B-A164-754BE967D3D7}" name="Table1" displayName="Table1" ref="A1:F622" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="1" tableBorderDxfId="0">
+  <autoFilter ref="A1:F622" xr:uid="{D5A367C9-9BB7-480B-A164-754BE967D3D7}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{EBEACA58-8E92-4785-BA2A-B6087B690D19}" name="Section"/>
     <tableColumn id="2" xr3:uid="{0FDF3B26-1ECF-47DE-B46D-651FCE06DC59}" name="Subsection"/>
@@ -2415,13 +2409,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:F632"/>
+  <dimension ref="A1:F622"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="28" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="1" max="1" width="43.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.36328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15.5" x14ac:dyDescent="0.35">
@@ -2881,10 +2877,10 @@
         <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="D29" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E29" t="s">
         <v>46</v>
@@ -2899,7 +2895,7 @@
         <v>9</v>
       </c>
       <c r="B30" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="D30" t="s">
         <v>73</v>
@@ -2917,7 +2913,7 @@
         <v>9</v>
       </c>
       <c r="B31" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="D31" t="s">
         <v>74</v>
@@ -2935,7 +2931,7 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="D32" t="s">
         <v>75</v>
@@ -2953,10 +2949,10 @@
         <v>9</v>
       </c>
       <c r="B33" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="C33" t="s">
-        <v>567</v>
+        <v>547</v>
       </c>
       <c r="D33" t="s">
         <v>76</v>
@@ -2974,10 +2970,10 @@
         <v>9</v>
       </c>
       <c r="B34" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="C34" t="s">
-        <v>567</v>
+        <v>547</v>
       </c>
       <c r="D34" t="s">
         <v>77</v>
@@ -2995,13 +2991,13 @@
         <v>9</v>
       </c>
       <c r="B35" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="C35" t="s">
-        <v>567</v>
+        <v>547</v>
       </c>
       <c r="D35" t="s">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="E35" t="s">
         <v>65</v>
@@ -3016,10 +3012,10 @@
         <v>9</v>
       </c>
       <c r="B36" t="s">
-        <v>556</v>
+        <v>536</v>
       </c>
       <c r="D36" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E36" t="s">
         <v>46</v>
@@ -3034,7 +3030,7 @@
         <v>9</v>
       </c>
       <c r="B37" t="s">
-        <v>556</v>
+        <v>536</v>
       </c>
       <c r="D37" t="s">
         <v>78</v>
@@ -3052,7 +3048,7 @@
         <v>9</v>
       </c>
       <c r="B38" t="s">
-        <v>556</v>
+        <v>536</v>
       </c>
       <c r="D38" t="s">
         <v>79</v>
@@ -3070,10 +3066,10 @@
         <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="D39" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E39" t="s">
         <v>46</v>
@@ -3088,7 +3084,7 @@
         <v>9</v>
       </c>
       <c r="B40" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="D40" t="s">
         <v>78</v>
@@ -3106,7 +3102,7 @@
         <v>9</v>
       </c>
       <c r="B41" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="D41" t="s">
         <v>79</v>
@@ -3124,7 +3120,7 @@
         <v>9</v>
       </c>
       <c r="B42" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="D42" t="s">
         <v>80</v>
@@ -3142,10 +3138,10 @@
         <v>9</v>
       </c>
       <c r="B43" t="s">
-        <v>557</v>
+        <v>537</v>
       </c>
       <c r="D43" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E43" t="s">
         <v>46</v>
@@ -3160,7 +3156,7 @@
         <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>557</v>
+        <v>537</v>
       </c>
       <c r="D44" t="s">
         <v>81</v>
@@ -3178,7 +3174,7 @@
         <v>9</v>
       </c>
       <c r="B45" t="s">
-        <v>557</v>
+        <v>537</v>
       </c>
       <c r="D45" t="s">
         <v>82</v>
@@ -3196,10 +3192,10 @@
         <v>9</v>
       </c>
       <c r="B46" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="D46" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E46" t="s">
         <v>46</v>
@@ -3214,7 +3210,7 @@
         <v>9</v>
       </c>
       <c r="B47" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="C47" t="s">
         <v>83</v>
@@ -3235,7 +3231,7 @@
         <v>9</v>
       </c>
       <c r="B48" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="C48" t="s">
         <v>83</v>
@@ -3256,7 +3252,7 @@
         <v>9</v>
       </c>
       <c r="B49" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="C49" t="s">
         <v>86</v>
@@ -3277,7 +3273,7 @@
         <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="C50" t="s">
         <v>86</v>
@@ -3298,7 +3294,7 @@
         <v>9</v>
       </c>
       <c r="B51" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="C51" t="s">
         <v>86</v>
@@ -3319,13 +3315,13 @@
         <v>9</v>
       </c>
       <c r="B52" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="C52" t="s">
         <v>86</v>
       </c>
       <c r="D52" t="s">
-        <v>569</v>
+        <v>549</v>
       </c>
       <c r="E52" t="s">
         <v>65</v>
@@ -3340,7 +3336,7 @@
         <v>9</v>
       </c>
       <c r="B53" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="C53" t="s">
         <v>86</v>
@@ -3361,10 +3357,10 @@
         <v>9</v>
       </c>
       <c r="B54" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="D54" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E54" t="s">
         <v>46</v>
@@ -3379,7 +3375,7 @@
         <v>9</v>
       </c>
       <c r="B55" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="C55" t="s">
         <v>83</v>
@@ -3400,7 +3396,7 @@
         <v>9</v>
       </c>
       <c r="B56" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="C56" t="s">
         <v>83</v>
@@ -3421,7 +3417,7 @@
         <v>9</v>
       </c>
       <c r="B57" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="C57" t="s">
         <v>86</v>
@@ -3442,7 +3438,7 @@
         <v>9</v>
       </c>
       <c r="B58" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="C58" t="s">
         <v>86</v>
@@ -3463,7 +3459,7 @@
         <v>9</v>
       </c>
       <c r="B59" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="C59" t="s">
         <v>86</v>
@@ -3484,7 +3480,7 @@
         <v>9</v>
       </c>
       <c r="B60" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
       <c r="C60" t="s">
         <v>86</v>
@@ -3505,7 +3501,7 @@
         <v>9</v>
       </c>
       <c r="D61" t="s">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="E61" t="s">
         <v>46</v>
@@ -3520,7 +3516,7 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>571</v>
+        <v>551</v>
       </c>
       <c r="E62" t="s">
         <v>46</v>
@@ -3535,10 +3531,10 @@
         <v>9</v>
       </c>
       <c r="B63" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="D63" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E63" t="s">
         <v>46</v>
@@ -3553,7 +3549,7 @@
         <v>9</v>
       </c>
       <c r="B64" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="D64" t="s">
         <v>93</v>
@@ -3571,7 +3567,7 @@
         <v>9</v>
       </c>
       <c r="B65" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="D65" t="s">
         <v>74</v>
@@ -3589,7 +3585,7 @@
         <v>9</v>
       </c>
       <c r="B66" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="D66" t="s">
         <v>94</v>
@@ -3607,10 +3603,10 @@
         <v>9</v>
       </c>
       <c r="B67" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="D67" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E67" t="s">
         <v>46</v>
@@ -3625,7 +3621,7 @@
         <v>9</v>
       </c>
       <c r="B68" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="D68" t="s">
         <v>95</v>
@@ -3643,7 +3639,7 @@
         <v>9</v>
       </c>
       <c r="B69" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="D69" t="s">
         <v>74</v>
@@ -3661,7 +3657,7 @@
         <v>9</v>
       </c>
       <c r="B70" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="D70" t="s">
         <v>75</v>
@@ -3679,10 +3675,10 @@
         <v>9</v>
       </c>
       <c r="B71" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="D71" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E71" t="s">
         <v>46</v>
@@ -3697,7 +3693,7 @@
         <v>9</v>
       </c>
       <c r="B72" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="D72" t="s">
         <v>96</v>
@@ -3715,7 +3711,7 @@
         <v>9</v>
       </c>
       <c r="B73" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="D73" t="s">
         <v>74</v>
@@ -3733,10 +3729,10 @@
         <v>9</v>
       </c>
       <c r="B74" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="D74" t="s">
-        <v>572</v>
+        <v>552</v>
       </c>
       <c r="E74" t="s">
         <v>46</v>
@@ -3751,10 +3747,10 @@
         <v>9</v>
       </c>
       <c r="B75" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="D75" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E75" t="s">
         <v>46</v>
@@ -3769,7 +3765,7 @@
         <v>9</v>
       </c>
       <c r="B76" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="D76" t="s">
         <v>78</v>
@@ -3787,7 +3783,7 @@
         <v>9</v>
       </c>
       <c r="B77" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="D77" t="s">
         <v>97</v>
@@ -3805,10 +3801,10 @@
         <v>9</v>
       </c>
       <c r="B78" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="D78" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="E78" t="s">
         <v>46</v>
@@ -3823,7 +3819,7 @@
         <v>9</v>
       </c>
       <c r="B79" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="D79" t="s">
         <v>98</v>
@@ -3841,7 +3837,7 @@
         <v>9</v>
       </c>
       <c r="B80" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="D80" t="s">
         <v>99</v>
@@ -3859,7 +3855,7 @@
         <v>9</v>
       </c>
       <c r="B81" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="D81" t="s">
         <v>100</v>
@@ -3877,7 +3873,7 @@
         <v>9</v>
       </c>
       <c r="B82" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="D82" t="s">
         <v>101</v>
@@ -3895,7 +3891,7 @@
         <v>9</v>
       </c>
       <c r="B83" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="D83" t="s">
         <v>102</v>
@@ -3916,7 +3912,7 @@
         <v>103</v>
       </c>
       <c r="D84" t="s">
-        <v>573</v>
+        <v>553</v>
       </c>
       <c r="E84" t="s">
         <v>65</v>
@@ -4114,7 +4110,7 @@
         <v>14</v>
       </c>
       <c r="B96" t="s">
-        <v>565</v>
+        <v>545</v>
       </c>
       <c r="D96" t="s">
         <v>106</v>
@@ -4132,7 +4128,7 @@
         <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>565</v>
+        <v>545</v>
       </c>
       <c r="D97" t="s">
         <v>107</v>
@@ -4438,7 +4434,7 @@
         <v>117</v>
       </c>
       <c r="C113" t="s">
-        <v>566</v>
+        <v>546</v>
       </c>
       <c r="D113" t="s">
         <v>128</v>
@@ -4459,7 +4455,7 @@
         <v>117</v>
       </c>
       <c r="C114" t="s">
-        <v>566</v>
+        <v>546</v>
       </c>
       <c r="D114" t="s">
         <v>129</v>
@@ -4480,10 +4476,10 @@
         <v>117</v>
       </c>
       <c r="C115" t="s">
-        <v>566</v>
+        <v>546</v>
       </c>
       <c r="D115" t="s">
-        <v>574</v>
+        <v>554</v>
       </c>
       <c r="E115" t="s">
         <v>65</v>
@@ -4501,7 +4497,7 @@
         <v>117</v>
       </c>
       <c r="C116" t="s">
-        <v>566</v>
+        <v>546</v>
       </c>
       <c r="D116" t="s">
         <v>130</v>
@@ -4522,7 +4518,7 @@
         <v>117</v>
       </c>
       <c r="C117" t="s">
-        <v>575</v>
+        <v>555</v>
       </c>
       <c r="D117" t="s">
         <v>106</v>
@@ -4543,7 +4539,7 @@
         <v>117</v>
       </c>
       <c r="C118" t="s">
-        <v>575</v>
+        <v>555</v>
       </c>
       <c r="D118" t="s">
         <v>107</v>
@@ -4618,7 +4614,7 @@
         <v>131</v>
       </c>
       <c r="D122" t="s">
-        <v>576</v>
+        <v>556</v>
       </c>
       <c r="E122" t="s">
         <v>65</v>
@@ -4815,11 +4811,8 @@
       <c r="B133" t="s">
         <v>145</v>
       </c>
-      <c r="C133" t="s">
-        <v>43</v>
-      </c>
       <c r="D133" t="s">
-        <v>146</v>
+        <v>557</v>
       </c>
       <c r="E133" t="s">
         <v>65</v>
@@ -4840,7 +4833,7 @@
         <v>43</v>
       </c>
       <c r="D134" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E134" t="s">
         <v>65</v>
@@ -4861,10 +4854,10 @@
         <v>43</v>
       </c>
       <c r="D135" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E135" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F135" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -4882,10 +4875,10 @@
         <v>43</v>
       </c>
       <c r="D136" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E136" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F136" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -4899,14 +4892,11 @@
       <c r="B137" t="s">
         <v>145</v>
       </c>
-      <c r="C137" t="s">
-        <v>43</v>
-      </c>
       <c r="D137" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E137" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F137" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -4920,14 +4910,11 @@
       <c r="B138" t="s">
         <v>145</v>
       </c>
-      <c r="C138" t="s">
-        <v>43</v>
-      </c>
       <c r="D138" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E138" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F138" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -4941,14 +4928,11 @@
       <c r="B139" t="s">
         <v>145</v>
       </c>
-      <c r="C139" t="s">
-        <v>43</v>
-      </c>
       <c r="D139" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E139" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F139" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -4962,11 +4946,8 @@
       <c r="B140" t="s">
         <v>145</v>
       </c>
-      <c r="C140" t="s">
-        <v>43</v>
-      </c>
       <c r="D140" t="s">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="E140" t="s">
         <v>46</v>
@@ -4981,13 +4962,13 @@
         <v>14</v>
       </c>
       <c r="B141" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="D141" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E141" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F141" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5002,7 +4983,7 @@
         <v>153</v>
       </c>
       <c r="D142" t="s">
-        <v>154</v>
+        <v>106</v>
       </c>
       <c r="E142" t="s">
         <v>65</v>
@@ -5017,7 +4998,7 @@
         <v>14</v>
       </c>
       <c r="B143" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="D143" t="s">
         <v>67</v>
@@ -5035,10 +5016,10 @@
         <v>14</v>
       </c>
       <c r="B144" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D144" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="E144" t="s">
         <v>65</v>
@@ -5053,10 +5034,10 @@
         <v>14</v>
       </c>
       <c r="B145" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="D145" t="s">
-        <v>158</v>
+        <v>67</v>
       </c>
       <c r="E145" t="s">
         <v>65</v>
@@ -5071,10 +5052,10 @@
         <v>14</v>
       </c>
       <c r="B146" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D146" t="s">
-        <v>159</v>
+        <v>67</v>
       </c>
       <c r="E146" t="s">
         <v>65</v>
@@ -5086,13 +5067,13 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B147" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D147" t="s">
-        <v>67</v>
+        <v>158</v>
       </c>
       <c r="E147" t="s">
         <v>65</v>
@@ -5104,13 +5085,13 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B148" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D148" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="E148" t="s">
         <v>65</v>
@@ -5122,13 +5103,13 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B149" t="s">
-        <v>160</v>
+        <v>558</v>
       </c>
       <c r="D149" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="E149" t="s">
         <v>65</v>
@@ -5140,13 +5121,13 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B150" t="s">
-        <v>160</v>
+        <v>558</v>
       </c>
       <c r="D150" t="s">
-        <v>163</v>
+        <v>559</v>
       </c>
       <c r="E150" t="s">
         <v>65</v>
@@ -5158,13 +5139,13 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B151" t="s">
-        <v>160</v>
+        <v>560</v>
       </c>
       <c r="D151" t="s">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="E151" t="s">
         <v>65</v>
@@ -5176,16 +5157,16 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B152" t="s">
-        <v>160</v>
+        <v>560</v>
       </c>
       <c r="D152" t="s">
-        <v>71</v>
+        <v>561</v>
       </c>
       <c r="E152" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F152" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5194,16 +5175,13 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>160</v>
+        <v>14</v>
       </c>
       <c r="D153" t="s">
-        <v>165</v>
+        <v>71</v>
       </c>
       <c r="E153" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F153" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5218,7 +5196,7 @@
         <v>160</v>
       </c>
       <c r="D154" t="s">
-        <v>166</v>
+        <v>67</v>
       </c>
       <c r="E154" t="s">
         <v>65</v>
@@ -5236,7 +5214,7 @@
         <v>160</v>
       </c>
       <c r="D155" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="E155" t="s">
         <v>65</v>
@@ -5251,10 +5229,10 @@
         <v>15</v>
       </c>
       <c r="B156" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D156" t="s">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="E156" t="s">
         <v>65</v>
@@ -5269,10 +5247,10 @@
         <v>15</v>
       </c>
       <c r="B157" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D157" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="E157" t="s">
         <v>65</v>
@@ -5287,10 +5265,10 @@
         <v>15</v>
       </c>
       <c r="B158" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D158" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="E158" t="s">
         <v>65</v>
@@ -5305,13 +5283,13 @@
         <v>15</v>
       </c>
       <c r="B159" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D159" t="s">
-        <v>171</v>
+        <v>71</v>
       </c>
       <c r="E159" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F159" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5323,10 +5301,10 @@
         <v>15</v>
       </c>
       <c r="B160" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D160" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E160" t="s">
         <v>65</v>
@@ -5341,10 +5319,10 @@
         <v>15</v>
       </c>
       <c r="B161" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D161" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E161" t="s">
         <v>65</v>
@@ -5359,10 +5337,10 @@
         <v>15</v>
       </c>
       <c r="B162" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D162" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E162" t="s">
         <v>65</v>
@@ -5380,7 +5358,7 @@
         <v>168</v>
       </c>
       <c r="D163" t="s">
-        <v>175</v>
+        <v>67</v>
       </c>
       <c r="E163" t="s">
         <v>65</v>
@@ -5398,7 +5376,7 @@
         <v>168</v>
       </c>
       <c r="D164" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E164" t="s">
         <v>65</v>
@@ -5416,7 +5394,7 @@
         <v>168</v>
       </c>
       <c r="D165" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="E165" t="s">
         <v>65</v>
@@ -5434,7 +5412,7 @@
         <v>168</v>
       </c>
       <c r="D166" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="E166" t="s">
         <v>65</v>
@@ -5452,7 +5430,7 @@
         <v>168</v>
       </c>
       <c r="D167" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E167" t="s">
         <v>65</v>
@@ -5470,10 +5448,10 @@
         <v>168</v>
       </c>
       <c r="D168" t="s">
-        <v>71</v>
+        <v>173</v>
       </c>
       <c r="E168" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F168" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5485,10 +5463,10 @@
         <v>15</v>
       </c>
       <c r="B169" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D169" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="E169" t="s">
         <v>65</v>
@@ -5503,10 +5481,10 @@
         <v>15</v>
       </c>
       <c r="B170" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D170" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E170" t="s">
         <v>65</v>
@@ -5521,10 +5499,10 @@
         <v>15</v>
       </c>
       <c r="B171" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D171" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E171" t="s">
         <v>65</v>
@@ -5539,10 +5517,10 @@
         <v>15</v>
       </c>
       <c r="B172" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D172" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="E172" t="s">
         <v>65</v>
@@ -5557,10 +5535,10 @@
         <v>15</v>
       </c>
       <c r="B173" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D173" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E173" t="s">
         <v>65</v>
@@ -5575,13 +5553,13 @@
         <v>15</v>
       </c>
       <c r="B174" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D174" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="E174" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F174" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5593,10 +5571,10 @@
         <v>15</v>
       </c>
       <c r="B175" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D175" t="s">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="E175" t="s">
         <v>46</v>
@@ -5614,10 +5592,10 @@
         <v>180</v>
       </c>
       <c r="D176" t="s">
-        <v>71</v>
+        <v>181</v>
       </c>
       <c r="E176" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F176" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5629,10 +5607,10 @@
         <v>15</v>
       </c>
       <c r="B177" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D177" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="E177" t="s">
         <v>65</v>
@@ -5647,10 +5625,10 @@
         <v>15</v>
       </c>
       <c r="B178" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D178" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="E178" t="s">
         <v>65</v>
@@ -5665,10 +5643,10 @@
         <v>15</v>
       </c>
       <c r="B179" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D179" t="s">
-        <v>189</v>
+        <v>170</v>
       </c>
       <c r="E179" t="s">
         <v>65</v>
@@ -5683,10 +5661,10 @@
         <v>15</v>
       </c>
       <c r="B180" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D180" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="E180" t="s">
         <v>65</v>
@@ -5701,13 +5679,13 @@
         <v>15</v>
       </c>
       <c r="B181" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D181" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="E181" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F181" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5719,13 +5697,13 @@
         <v>15</v>
       </c>
       <c r="B182" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D182" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="E182" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F182" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5737,13 +5715,13 @@
         <v>15</v>
       </c>
       <c r="B183" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D183" t="s">
-        <v>193</v>
+        <v>71</v>
       </c>
       <c r="E183" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F183" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5758,7 +5736,7 @@
         <v>186</v>
       </c>
       <c r="D184" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="E184" t="s">
         <v>65</v>
@@ -5776,7 +5754,7 @@
         <v>186</v>
       </c>
       <c r="D185" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="E185" t="s">
         <v>65</v>
@@ -5794,10 +5772,10 @@
         <v>186</v>
       </c>
       <c r="D186" t="s">
-        <v>71</v>
+        <v>189</v>
       </c>
       <c r="E186" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F186" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5809,10 +5787,10 @@
         <v>15</v>
       </c>
       <c r="B187" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D187" t="s">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="E187" t="s">
         <v>65</v>
@@ -5827,10 +5805,10 @@
         <v>15</v>
       </c>
       <c r="B188" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D188" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="E188" t="s">
         <v>65</v>
@@ -5845,10 +5823,10 @@
         <v>15</v>
       </c>
       <c r="B189" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D189" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="E189" t="s">
         <v>65</v>
@@ -5863,10 +5841,10 @@
         <v>15</v>
       </c>
       <c r="B190" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D190" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="E190" t="s">
         <v>65</v>
@@ -5881,10 +5859,10 @@
         <v>15</v>
       </c>
       <c r="B191" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D191" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="E191" t="s">
         <v>65</v>
@@ -5899,10 +5877,10 @@
         <v>15</v>
       </c>
       <c r="B192" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D192" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="E192" t="s">
         <v>65</v>
@@ -5917,13 +5895,13 @@
         <v>15</v>
       </c>
       <c r="B193" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D193" t="s">
-        <v>203</v>
+        <v>71</v>
       </c>
       <c r="E193" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F193" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -5938,7 +5916,7 @@
         <v>196</v>
       </c>
       <c r="D194" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="E194" t="s">
         <v>65</v>
@@ -5956,7 +5934,7 @@
         <v>196</v>
       </c>
       <c r="D195" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E195" t="s">
         <v>65</v>
@@ -5974,7 +5952,7 @@
         <v>196</v>
       </c>
       <c r="D196" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="E196" t="s">
         <v>65</v>
@@ -5992,10 +5970,10 @@
         <v>196</v>
       </c>
       <c r="D197" t="s">
-        <v>71</v>
+        <v>200</v>
       </c>
       <c r="E197" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F197" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -6004,13 +5982,13 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A198" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B198" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D198" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="E198" t="s">
         <v>65</v>
@@ -6022,13 +6000,13 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A199" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B199" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D199" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="E199" t="s">
         <v>65</v>
@@ -6040,13 +6018,13 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A200" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B200" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D200" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E200" t="s">
         <v>65</v>
@@ -6058,13 +6036,13 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A201" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B201" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D201" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="E201" t="s">
         <v>65</v>
@@ -6076,13 +6054,13 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A202" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B202" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D202" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E202" t="s">
         <v>65</v>
@@ -6094,13 +6072,13 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B203" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D203" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="E203" t="s">
         <v>65</v>
@@ -6112,16 +6090,16 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A204" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B204" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="D204" t="s">
-        <v>202</v>
+        <v>71</v>
       </c>
       <c r="E204" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F204" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -6136,7 +6114,7 @@
         <v>207</v>
       </c>
       <c r="D205" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="E205" t="s">
         <v>65</v>
@@ -6151,10 +6129,10 @@
         <v>16</v>
       </c>
       <c r="B206" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D206" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E206" t="s">
         <v>65</v>
@@ -6169,10 +6147,10 @@
         <v>16</v>
       </c>
       <c r="B207" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D207" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E207" t="s">
         <v>65</v>
@@ -6187,10 +6165,10 @@
         <v>16</v>
       </c>
       <c r="B208" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D208" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="E208" t="s">
         <v>65</v>
@@ -6205,10 +6183,10 @@
         <v>16</v>
       </c>
       <c r="B209" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D209" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E209" t="s">
         <v>65</v>
@@ -6223,10 +6201,10 @@
         <v>16</v>
       </c>
       <c r="B210" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D210" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="E210" t="s">
         <v>65</v>
@@ -6241,10 +6219,10 @@
         <v>16</v>
       </c>
       <c r="B211" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D211" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="E211" t="s">
         <v>65</v>
@@ -6259,10 +6237,10 @@
         <v>16</v>
       </c>
       <c r="B212" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="D212" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="E212" t="s">
         <v>65</v>
@@ -6280,7 +6258,7 @@
         <v>215</v>
       </c>
       <c r="D213" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
       <c r="E213" t="s">
         <v>65</v>
@@ -6298,7 +6276,7 @@
         <v>215</v>
       </c>
       <c r="D214" t="s">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="E214" t="s">
         <v>65</v>
@@ -6316,7 +6294,7 @@
         <v>215</v>
       </c>
       <c r="D215" t="s">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="E215" t="s">
         <v>65</v>
@@ -6334,7 +6312,7 @@
         <v>215</v>
       </c>
       <c r="D216" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E216" t="s">
         <v>65</v>
@@ -6352,7 +6330,7 @@
         <v>215</v>
       </c>
       <c r="D217" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="E217" t="s">
         <v>65</v>
@@ -6370,7 +6348,7 @@
         <v>215</v>
       </c>
       <c r="D218" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E218" t="s">
         <v>65</v>
@@ -6388,7 +6366,7 @@
         <v>215</v>
       </c>
       <c r="D219" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
       <c r="E219" t="s">
         <v>65</v>
@@ -6406,7 +6384,7 @@
         <v>215</v>
       </c>
       <c r="D220" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="E220" t="s">
         <v>65</v>
@@ -6424,7 +6402,7 @@
         <v>215</v>
       </c>
       <c r="D221" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="E221" t="s">
         <v>65</v>
@@ -6442,7 +6420,7 @@
         <v>215</v>
       </c>
       <c r="D222" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E222" t="s">
         <v>65</v>
@@ -6460,7 +6438,7 @@
         <v>215</v>
       </c>
       <c r="D223" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="E223" t="s">
         <v>65</v>
@@ -6478,10 +6456,10 @@
         <v>215</v>
       </c>
       <c r="D224" t="s">
-        <v>71</v>
+        <v>227</v>
       </c>
       <c r="E224" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F224" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -6490,13 +6468,13 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B225" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="D225" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E225" t="s">
         <v>65</v>
@@ -6508,13 +6486,13 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B226" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="D226" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="E226" t="s">
         <v>65</v>
@@ -6526,13 +6504,13 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B227" t="s">
-        <v>234</v>
+        <v>215</v>
       </c>
       <c r="D227" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E227" t="s">
         <v>65</v>
@@ -6544,13 +6522,13 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B228" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="D228" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E228" t="s">
         <v>65</v>
@@ -6562,13 +6540,13 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A229" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B229" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="D229" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="E229" t="s">
         <v>65</v>
@@ -6580,13 +6558,13 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B230" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="D230" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="E230" t="s">
         <v>65</v>
@@ -6598,16 +6576,16 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B231" t="s">
-        <v>238</v>
+        <v>215</v>
       </c>
       <c r="D231" t="s">
-        <v>240</v>
+        <v>71</v>
       </c>
       <c r="E231" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F231" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -6619,10 +6597,10 @@
         <v>17</v>
       </c>
       <c r="B232" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D232" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="E232" t="s">
         <v>65</v>
@@ -6637,10 +6615,10 @@
         <v>17</v>
       </c>
       <c r="B233" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D233" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="E233" t="s">
         <v>65</v>
@@ -6655,10 +6633,10 @@
         <v>17</v>
       </c>
       <c r="B234" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="D234" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="E234" t="s">
         <v>65</v>
@@ -6673,10 +6651,10 @@
         <v>17</v>
       </c>
       <c r="B235" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D235" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="E235" t="s">
         <v>65</v>
@@ -6691,10 +6669,10 @@
         <v>17</v>
       </c>
       <c r="B236" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D236" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="E236" t="s">
         <v>65</v>
@@ -6709,10 +6687,10 @@
         <v>17</v>
       </c>
       <c r="B237" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D237" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="E237" t="s">
         <v>65</v>
@@ -6727,10 +6705,10 @@
         <v>17</v>
       </c>
       <c r="B238" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="D238" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="E238" t="s">
         <v>65</v>
@@ -6745,10 +6723,10 @@
         <v>17</v>
       </c>
       <c r="B239" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D239" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="E239" t="s">
         <v>65</v>
@@ -6763,10 +6741,10 @@
         <v>17</v>
       </c>
       <c r="B240" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D240" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="E240" t="s">
         <v>65</v>
@@ -6781,13 +6759,13 @@
         <v>17</v>
       </c>
       <c r="B241" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D241" t="s">
-        <v>71</v>
+        <v>244</v>
       </c>
       <c r="E241" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F241" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -6796,13 +6774,13 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A242" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B242" t="s">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="D242" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="E242" t="s">
         <v>65</v>
@@ -6814,13 +6792,13 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A243" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B243" t="s">
-        <v>43</v>
+        <v>245</v>
       </c>
       <c r="D243" t="s">
-        <v>158</v>
+        <v>247</v>
       </c>
       <c r="E243" t="s">
         <v>65</v>
@@ -6832,13 +6810,13 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A244" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B244" t="s">
-        <v>43</v>
+        <v>245</v>
       </c>
       <c r="D244" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="E244" t="s">
         <v>65</v>
@@ -6850,13 +6828,13 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A245" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B245" t="s">
-        <v>43</v>
+        <v>245</v>
       </c>
       <c r="D245" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E245" t="s">
         <v>65</v>
@@ -6868,16 +6846,16 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A246" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B246" t="s">
-        <v>43</v>
+        <v>245</v>
       </c>
       <c r="D246" t="s">
-        <v>75</v>
+        <v>250</v>
       </c>
       <c r="E246" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F246" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -6886,16 +6864,16 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A247" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B247" t="s">
-        <v>43</v>
+        <v>245</v>
       </c>
       <c r="D247" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E247" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="F247" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -6904,16 +6882,16 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A248" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B248" t="s">
-        <v>43</v>
+        <v>245</v>
       </c>
       <c r="D248" t="s">
-        <v>257</v>
+        <v>71</v>
       </c>
       <c r="E248" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F248" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -6925,10 +6903,10 @@
         <v>18</v>
       </c>
       <c r="B249" t="s">
-        <v>43</v>
+        <v>252</v>
       </c>
       <c r="D249" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="E249" t="s">
         <v>65</v>
@@ -6943,13 +6921,13 @@
         <v>18</v>
       </c>
       <c r="B250" t="s">
-        <v>259</v>
+        <v>43</v>
       </c>
       <c r="D250" t="s">
-        <v>260</v>
+        <v>158</v>
       </c>
       <c r="E250" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="F250" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -6961,13 +6939,13 @@
         <v>18</v>
       </c>
       <c r="B251" t="s">
-        <v>259</v>
+        <v>43</v>
       </c>
       <c r="D251" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="E251" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="F251" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -6979,13 +6957,13 @@
         <v>18</v>
       </c>
       <c r="B252" t="s">
-        <v>259</v>
+        <v>43</v>
       </c>
       <c r="D252" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="E252" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="F252" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -6997,13 +6975,13 @@
         <v>18</v>
       </c>
       <c r="B253" t="s">
-        <v>259</v>
+        <v>43</v>
       </c>
       <c r="D253" t="s">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="E253" t="s">
-        <v>143</v>
+        <v>46</v>
       </c>
       <c r="F253" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7015,10 +6993,10 @@
         <v>18</v>
       </c>
       <c r="B254" t="s">
-        <v>259</v>
+        <v>43</v>
       </c>
       <c r="D254" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="E254" t="s">
         <v>143</v>
@@ -7033,13 +7011,13 @@
         <v>18</v>
       </c>
       <c r="B255" t="s">
-        <v>259</v>
+        <v>43</v>
       </c>
       <c r="D255" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="E255" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="F255" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7051,13 +7029,13 @@
         <v>18</v>
       </c>
       <c r="B256" t="s">
-        <v>259</v>
+        <v>43</v>
       </c>
       <c r="D256" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="E256" t="s">
-        <v>143</v>
+        <v>65</v>
       </c>
       <c r="F256" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7072,7 +7050,7 @@
         <v>259</v>
       </c>
       <c r="D257" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="E257" t="s">
         <v>143</v>
@@ -7090,10 +7068,10 @@
         <v>259</v>
       </c>
       <c r="D258" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="E258" t="s">
-        <v>65</v>
+        <v>143</v>
       </c>
       <c r="F258" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7105,13 +7083,13 @@
         <v>18</v>
       </c>
       <c r="B259" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D259" t="s">
-        <v>67</v>
+        <v>262</v>
       </c>
       <c r="E259" t="s">
-        <v>65</v>
+        <v>143</v>
       </c>
       <c r="F259" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7123,13 +7101,13 @@
         <v>18</v>
       </c>
       <c r="B260" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D260" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="E260" t="s">
-        <v>65</v>
+        <v>143</v>
       </c>
       <c r="F260" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7141,13 +7119,13 @@
         <v>18</v>
       </c>
       <c r="B261" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D261" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="E261" t="s">
-        <v>65</v>
+        <v>143</v>
       </c>
       <c r="F261" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7159,13 +7137,13 @@
         <v>18</v>
       </c>
       <c r="B262" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D262" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="E262" t="s">
-        <v>46</v>
+        <v>143</v>
       </c>
       <c r="F262" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7177,13 +7155,13 @@
         <v>18</v>
       </c>
       <c r="B263" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="D263" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="E263" t="s">
-        <v>65</v>
+        <v>143</v>
       </c>
       <c r="F263" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7195,13 +7173,13 @@
         <v>18</v>
       </c>
       <c r="B264" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="D264" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="E264" t="s">
-        <v>65</v>
+        <v>143</v>
       </c>
       <c r="F264" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7213,10 +7191,10 @@
         <v>18</v>
       </c>
       <c r="B265" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
       <c r="D265" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="E265" t="s">
         <v>65</v>
@@ -7231,10 +7209,10 @@
         <v>18</v>
       </c>
       <c r="B266" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D266" t="s">
-        <v>277</v>
+        <v>67</v>
       </c>
       <c r="E266" t="s">
         <v>65</v>
@@ -7249,10 +7227,10 @@
         <v>18</v>
       </c>
       <c r="B267" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D267" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="E267" t="s">
         <v>65</v>
@@ -7267,10 +7245,10 @@
         <v>18</v>
       </c>
       <c r="B268" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D268" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="E268" t="s">
         <v>65</v>
@@ -7285,7 +7263,7 @@
         <v>18</v>
       </c>
       <c r="B269" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D269" t="s">
         <v>272</v>
@@ -7303,10 +7281,10 @@
         <v>18</v>
       </c>
       <c r="B270" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="D270" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="E270" t="s">
         <v>65</v>
@@ -7321,10 +7299,10 @@
         <v>18</v>
       </c>
       <c r="B271" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D271" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="E271" t="s">
         <v>65</v>
@@ -7339,10 +7317,10 @@
         <v>18</v>
       </c>
       <c r="B272" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D272" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="E272" t="s">
         <v>65</v>
@@ -7357,10 +7335,10 @@
         <v>18</v>
       </c>
       <c r="B273" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D273" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="E273" t="s">
         <v>65</v>
@@ -7375,10 +7353,10 @@
         <v>18</v>
       </c>
       <c r="B274" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D274" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E274" t="s">
         <v>65</v>
@@ -7393,10 +7371,10 @@
         <v>18</v>
       </c>
       <c r="B275" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D275" t="s">
-        <v>286</v>
+        <v>574</v>
       </c>
       <c r="E275" t="s">
         <v>65</v>
@@ -7411,13 +7389,13 @@
         <v>18</v>
       </c>
       <c r="B276" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="D276" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
       <c r="E276" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F276" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7429,10 +7407,10 @@
         <v>18</v>
       </c>
       <c r="B277" t="s">
-        <v>280</v>
+        <v>569</v>
       </c>
       <c r="D277" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="E277" t="s">
         <v>65</v>
@@ -7447,10 +7425,10 @@
         <v>18</v>
       </c>
       <c r="B278" t="s">
+        <v>569</v>
+      </c>
+      <c r="D278" t="s">
         <v>280</v>
-      </c>
-      <c r="D278" t="s">
-        <v>235</v>
       </c>
       <c r="E278" t="s">
         <v>65</v>
@@ -7465,10 +7443,10 @@
         <v>18</v>
       </c>
       <c r="B279" t="s">
-        <v>289</v>
+        <v>569</v>
       </c>
       <c r="D279" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E279" t="s">
         <v>65</v>
@@ -7483,10 +7461,10 @@
         <v>18</v>
       </c>
       <c r="B280" t="s">
-        <v>291</v>
+        <v>569</v>
       </c>
       <c r="D280" t="s">
-        <v>67</v>
+        <v>282</v>
       </c>
       <c r="E280" t="s">
         <v>65</v>
@@ -7501,10 +7479,10 @@
         <v>18</v>
       </c>
       <c r="B281" t="s">
-        <v>291</v>
+        <v>569</v>
       </c>
       <c r="D281" t="s">
-        <v>292</v>
+        <v>570</v>
       </c>
       <c r="E281" t="s">
         <v>65</v>
@@ -7519,10 +7497,10 @@
         <v>18</v>
       </c>
       <c r="B282" t="s">
-        <v>291</v>
+        <v>569</v>
       </c>
       <c r="D282" t="s">
-        <v>293</v>
+        <v>571</v>
       </c>
       <c r="E282" t="s">
         <v>65</v>
@@ -7537,13 +7515,13 @@
         <v>18</v>
       </c>
       <c r="B283" t="s">
-        <v>291</v>
+        <v>569</v>
       </c>
       <c r="D283" t="s">
-        <v>294</v>
+        <v>568</v>
       </c>
       <c r="E283" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F283" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7555,10 +7533,10 @@
         <v>18</v>
       </c>
       <c r="B284" t="s">
-        <v>295</v>
+        <v>569</v>
       </c>
       <c r="D284" t="s">
-        <v>67</v>
+        <v>572</v>
       </c>
       <c r="E284" t="s">
         <v>65</v>
@@ -7573,10 +7551,10 @@
         <v>18</v>
       </c>
       <c r="B285" t="s">
-        <v>295</v>
+        <v>569</v>
       </c>
       <c r="D285" t="s">
-        <v>296</v>
+        <v>573</v>
       </c>
       <c r="E285" t="s">
         <v>65</v>
@@ -7591,10 +7569,10 @@
         <v>18</v>
       </c>
       <c r="B286" t="s">
-        <v>295</v>
+        <v>569</v>
       </c>
       <c r="D286" t="s">
-        <v>297</v>
+        <v>235</v>
       </c>
       <c r="E286" t="s">
         <v>65</v>
@@ -7609,10 +7587,10 @@
         <v>18</v>
       </c>
       <c r="B287" t="s">
-        <v>295</v>
+        <v>283</v>
       </c>
       <c r="D287" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="E287" t="s">
         <v>65</v>
@@ -7627,10 +7605,10 @@
         <v>18</v>
       </c>
       <c r="B288" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D288" t="s">
-        <v>299</v>
+        <v>67</v>
       </c>
       <c r="E288" t="s">
         <v>65</v>
@@ -7645,10 +7623,10 @@
         <v>18</v>
       </c>
       <c r="B289" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D289" t="s">
-        <v>243</v>
+        <v>286</v>
       </c>
       <c r="E289" t="s">
         <v>65</v>
@@ -7663,10 +7641,10 @@
         <v>18</v>
       </c>
       <c r="B290" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D290" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="E290" t="s">
         <v>65</v>
@@ -7681,13 +7659,13 @@
         <v>18</v>
       </c>
       <c r="B291" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D291" t="s">
-        <v>111</v>
+        <v>288</v>
       </c>
       <c r="E291" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F291" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7699,10 +7677,10 @@
         <v>18</v>
       </c>
       <c r="B292" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D292" t="s">
-        <v>246</v>
+        <v>67</v>
       </c>
       <c r="E292" t="s">
         <v>65</v>
@@ -7717,10 +7695,10 @@
         <v>18</v>
       </c>
       <c r="B293" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D293" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="E293" t="s">
         <v>65</v>
@@ -7735,13 +7713,13 @@
         <v>18</v>
       </c>
       <c r="B294" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D294" t="s">
-        <v>75</v>
+        <v>291</v>
       </c>
       <c r="E294" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F294" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7753,10 +7731,10 @@
         <v>18</v>
       </c>
       <c r="B295" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D295" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="E295" t="s">
         <v>65</v>
@@ -7771,13 +7749,13 @@
         <v>18</v>
       </c>
       <c r="B296" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
       <c r="D296" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="E296" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F296" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7789,10 +7767,10 @@
         <v>18</v>
       </c>
       <c r="B297" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="D297" t="s">
-        <v>67</v>
+        <v>243</v>
       </c>
       <c r="E297" t="s">
         <v>65</v>
@@ -7807,10 +7785,10 @@
         <v>18</v>
       </c>
       <c r="B298" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="D298" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E298" t="s">
         <v>65</v>
@@ -7825,10 +7803,10 @@
         <v>18</v>
       </c>
       <c r="B299" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
       <c r="D299" t="s">
-        <v>305</v>
+        <v>111</v>
       </c>
       <c r="E299" t="s">
         <v>65</v>
@@ -7843,10 +7821,10 @@
         <v>18</v>
       </c>
       <c r="B300" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="D300" t="s">
-        <v>67</v>
+        <v>246</v>
       </c>
       <c r="E300" t="s">
         <v>65</v>
@@ -7861,10 +7839,10 @@
         <v>18</v>
       </c>
       <c r="B301" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="D301" t="s">
-        <v>307</v>
+        <v>295</v>
       </c>
       <c r="E301" t="s">
         <v>65</v>
@@ -7879,13 +7857,13 @@
         <v>18</v>
       </c>
       <c r="B302" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="D302" t="s">
-        <v>308</v>
+        <v>75</v>
       </c>
       <c r="E302" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F302" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7897,13 +7875,13 @@
         <v>18</v>
       </c>
       <c r="B303" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="D303" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="E303" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F303" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7915,10 +7893,10 @@
         <v>18</v>
       </c>
       <c r="B304" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="D304" t="s">
-        <v>311</v>
+        <v>288</v>
       </c>
       <c r="E304" t="s">
         <v>46</v>
@@ -7933,13 +7911,13 @@
         <v>18</v>
       </c>
       <c r="B305" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="D305" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E305" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F305" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -7948,10 +7926,13 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A306" t="s">
-        <v>19</v>
+        <v>18</v>
+      </c>
+      <c r="B306" t="s">
+        <v>297</v>
       </c>
       <c r="D306" t="s">
-        <v>67</v>
+        <v>298</v>
       </c>
       <c r="E306" t="s">
         <v>65</v>
@@ -7963,13 +7944,13 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A307" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B307" t="s">
-        <v>43</v>
+        <v>297</v>
       </c>
       <c r="D307" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="E307" t="s">
         <v>65</v>
@@ -7981,13 +7962,13 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A308" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B308" t="s">
-        <v>43</v>
+        <v>300</v>
       </c>
       <c r="D308" t="s">
-        <v>313</v>
+        <v>67</v>
       </c>
       <c r="E308" t="s">
         <v>65</v>
@@ -7999,13 +7980,13 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A309" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B309" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="D309" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
       <c r="E309" t="s">
         <v>65</v>
@@ -8017,13 +7998,13 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A310" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B310" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="D310" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="E310" t="s">
         <v>65</v>
@@ -8035,16 +8016,16 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A311" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B311" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
       <c r="D311" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="E311" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F311" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8053,16 +8034,16 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A312" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B312" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D312" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="E312" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F312" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8071,13 +8052,13 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A313" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B313" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="D313" t="s">
-        <v>272</v>
+        <v>71</v>
       </c>
       <c r="E313" t="s">
         <v>46</v>
@@ -8091,14 +8072,11 @@
       <c r="A314" t="s">
         <v>19</v>
       </c>
-      <c r="B314" t="s">
-        <v>314</v>
-      </c>
       <c r="D314" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E314" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F314" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8107,10 +8085,13 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A315" t="s">
-        <v>20</v>
+        <v>19</v>
+      </c>
+      <c r="B315" t="s">
+        <v>43</v>
       </c>
       <c r="D315" t="s">
-        <v>67</v>
+        <v>306</v>
       </c>
       <c r="E315" t="s">
         <v>65</v>
@@ -8122,13 +8103,13 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A316" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B316" t="s">
         <v>43</v>
       </c>
       <c r="D316" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="E316" t="s">
         <v>65</v>
@@ -8140,13 +8121,13 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A317" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B317" t="s">
-        <v>43</v>
+        <v>308</v>
       </c>
       <c r="D317" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="E317" t="s">
         <v>65</v>
@@ -8158,13 +8139,13 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A318" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B318" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="D318" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="E318" t="s">
         <v>65</v>
@@ -8176,13 +8157,13 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A319" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B319" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="D319" t="s">
-        <v>164</v>
+        <v>311</v>
       </c>
       <c r="E319" t="s">
         <v>65</v>
@@ -8194,13 +8175,13 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A320" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B320" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="D320" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="E320" t="s">
         <v>65</v>
@@ -8212,16 +8193,16 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A321" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B321" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="D321" t="s">
-        <v>324</v>
+        <v>272</v>
       </c>
       <c r="E321" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F321" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8230,10 +8211,10 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A322" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B322" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="D322" t="s">
         <v>71</v>
@@ -8248,7 +8229,7 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A323" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D323" t="s">
         <v>67</v>
@@ -8263,13 +8244,13 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A324" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B324" t="s">
-        <v>325</v>
+        <v>43</v>
       </c>
       <c r="D324" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="E324" t="s">
         <v>65</v>
@@ -8281,13 +8262,13 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A325" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B325" t="s">
-        <v>325</v>
+        <v>43</v>
       </c>
       <c r="D325" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="E325" t="s">
         <v>65</v>
@@ -8299,13 +8280,13 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A326" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B326" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="D326" t="s">
-        <v>106</v>
+        <v>316</v>
       </c>
       <c r="E326" t="s">
         <v>65</v>
@@ -8317,13 +8298,13 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A327" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B327" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="D327" t="s">
-        <v>67</v>
+        <v>164</v>
       </c>
       <c r="E327" t="s">
         <v>65</v>
@@ -8335,16 +8316,16 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A328" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B328" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="D328" t="s">
-        <v>71</v>
+        <v>317</v>
       </c>
       <c r="E328" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F328" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8353,13 +8334,13 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A329" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B329" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="D329" t="s">
-        <v>330</v>
+        <v>318</v>
       </c>
       <c r="E329" t="s">
         <v>65</v>
@@ -8371,16 +8352,16 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A330" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B330" t="s">
-        <v>329</v>
+        <v>315</v>
       </c>
       <c r="D330" t="s">
-        <v>331</v>
+        <v>71</v>
       </c>
       <c r="E330" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F330" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8389,13 +8370,10 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A331" t="s">
-        <v>22</v>
-      </c>
-      <c r="B331" t="s">
-        <v>329</v>
+        <v>21</v>
       </c>
       <c r="D331" t="s">
-        <v>332</v>
+        <v>67</v>
       </c>
       <c r="E331" t="s">
         <v>65</v>
@@ -8407,13 +8385,13 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A332" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B332" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="D332" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="E332" t="s">
         <v>65</v>
@@ -8425,13 +8403,13 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A333" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B333" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="D333" t="s">
-        <v>271</v>
+        <v>321</v>
       </c>
       <c r="E333" t="s">
         <v>65</v>
@@ -8443,16 +8421,16 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A334" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B334" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="D334" t="s">
-        <v>272</v>
+        <v>106</v>
       </c>
       <c r="E334" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F334" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8461,16 +8439,16 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A335" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B335" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="D335" t="s">
-        <v>294</v>
+        <v>67</v>
       </c>
       <c r="E335" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F335" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8479,16 +8457,16 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A336" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B336" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="D336" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E336" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F336" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8500,10 +8478,10 @@
         <v>22</v>
       </c>
       <c r="B337" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D337" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="E337" t="s">
         <v>65</v>
@@ -8518,10 +8496,10 @@
         <v>22</v>
       </c>
       <c r="B338" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D338" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="E338" t="s">
         <v>65</v>
@@ -8536,10 +8514,10 @@
         <v>22</v>
       </c>
       <c r="B339" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D339" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="E339" t="s">
         <v>65</v>
@@ -8554,10 +8532,10 @@
         <v>22</v>
       </c>
       <c r="B340" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D340" t="s">
-        <v>163</v>
+        <v>327</v>
       </c>
       <c r="E340" t="s">
         <v>65</v>
@@ -8572,10 +8550,10 @@
         <v>22</v>
       </c>
       <c r="B341" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D341" t="s">
-        <v>323</v>
+        <v>271</v>
       </c>
       <c r="E341" t="s">
         <v>65</v>
@@ -8590,10 +8568,10 @@
         <v>22</v>
       </c>
       <c r="B342" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="D342" t="s">
-        <v>294</v>
+        <v>272</v>
       </c>
       <c r="E342" t="s">
         <v>46</v>
@@ -8608,13 +8586,13 @@
         <v>22</v>
       </c>
       <c r="B343" t="s">
-        <v>337</v>
+        <v>323</v>
       </c>
       <c r="D343" t="s">
-        <v>67</v>
+        <v>288</v>
       </c>
       <c r="E343" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F343" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8626,10 +8604,10 @@
         <v>22</v>
       </c>
       <c r="B344" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D344" t="s">
-        <v>164</v>
+        <v>67</v>
       </c>
       <c r="E344" t="s">
         <v>65</v>
@@ -8644,10 +8622,10 @@
         <v>22</v>
       </c>
       <c r="B345" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D345" t="s">
-        <v>158</v>
+        <v>327</v>
       </c>
       <c r="E345" t="s">
         <v>65</v>
@@ -8662,10 +8640,10 @@
         <v>22</v>
       </c>
       <c r="B346" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D346" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="E346" t="s">
         <v>65</v>
@@ -8680,13 +8658,13 @@
         <v>22</v>
       </c>
       <c r="B347" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D347" t="s">
-        <v>71</v>
+        <v>330</v>
       </c>
       <c r="E347" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F347" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8698,13 +8676,13 @@
         <v>22</v>
       </c>
       <c r="B348" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
       <c r="D348" t="s">
-        <v>71</v>
+        <v>163</v>
       </c>
       <c r="E348" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F348" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8713,13 +8691,13 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A349" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B349" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="D349" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="E349" t="s">
         <v>65</v>
@@ -8731,16 +8709,16 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A350" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B350" t="s">
-        <v>339</v>
+        <v>328</v>
       </c>
       <c r="D350" t="s">
-        <v>331</v>
+        <v>288</v>
       </c>
       <c r="E350" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F350" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8749,13 +8727,13 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A351" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B351" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D351" t="s">
-        <v>271</v>
+        <v>67</v>
       </c>
       <c r="E351" t="s">
         <v>65</v>
@@ -8767,13 +8745,13 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A352" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B352" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D352" t="s">
-        <v>340</v>
+        <v>164</v>
       </c>
       <c r="E352" t="s">
         <v>65</v>
@@ -8785,13 +8763,13 @@
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A353" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B353" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D353" t="s">
-        <v>341</v>
+        <v>158</v>
       </c>
       <c r="E353" t="s">
         <v>65</v>
@@ -8803,13 +8781,13 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A354" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B354" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D354" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E354" t="s">
         <v>65</v>
@@ -8821,16 +8799,16 @@
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A355" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B355" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D355" t="s">
-        <v>343</v>
+        <v>71</v>
       </c>
       <c r="E355" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F355" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8839,16 +8817,16 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A356" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B356" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D356" t="s">
-        <v>344</v>
+        <v>71</v>
       </c>
       <c r="E356" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F356" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8860,13 +8838,13 @@
         <v>23</v>
       </c>
       <c r="B357" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D357" t="s">
-        <v>272</v>
+        <v>324</v>
       </c>
       <c r="E357" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F357" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8878,10 +8856,10 @@
         <v>23</v>
       </c>
       <c r="B358" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D358" t="s">
-        <v>345</v>
+        <v>325</v>
       </c>
       <c r="E358" t="s">
         <v>65</v>
@@ -8896,13 +8874,13 @@
         <v>23</v>
       </c>
       <c r="B359" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="D359" t="s">
-        <v>294</v>
+        <v>271</v>
       </c>
       <c r="E359" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F359" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -8914,10 +8892,10 @@
         <v>23</v>
       </c>
       <c r="B360" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D360" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="E360" t="s">
         <v>65</v>
@@ -8932,10 +8910,10 @@
         <v>23</v>
       </c>
       <c r="B361" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D361" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="E361" t="s">
         <v>65</v>
@@ -8950,10 +8928,10 @@
         <v>23</v>
       </c>
       <c r="B362" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D362" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="E362" t="s">
         <v>65</v>
@@ -8968,10 +8946,10 @@
         <v>23</v>
       </c>
       <c r="B363" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D363" t="s">
-        <v>349</v>
+        <v>337</v>
       </c>
       <c r="E363" t="s">
         <v>65</v>
@@ -8986,10 +8964,10 @@
         <v>23</v>
       </c>
       <c r="B364" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D364" t="s">
-        <v>350</v>
+        <v>338</v>
       </c>
       <c r="E364" t="s">
         <v>65</v>
@@ -9004,7 +8982,7 @@
         <v>23</v>
       </c>
       <c r="B365" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D365" t="s">
         <v>272</v>
@@ -9022,13 +9000,13 @@
         <v>23</v>
       </c>
       <c r="B366" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D366" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="E366" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F366" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9040,10 +9018,10 @@
         <v>23</v>
       </c>
       <c r="B367" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D367" t="s">
-        <v>352</v>
+        <v>288</v>
       </c>
       <c r="E367" t="s">
         <v>46</v>
@@ -9058,13 +9036,13 @@
         <v>23</v>
       </c>
       <c r="B368" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D368" t="s">
-        <v>294</v>
+        <v>341</v>
       </c>
       <c r="E368" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F368" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9076,10 +9054,10 @@
         <v>23</v>
       </c>
       <c r="B369" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D369" t="s">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="E369" t="s">
         <v>65</v>
@@ -9094,10 +9072,10 @@
         <v>23</v>
       </c>
       <c r="B370" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D370" t="s">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="E370" t="s">
         <v>65</v>
@@ -9112,10 +9090,10 @@
         <v>23</v>
       </c>
       <c r="B371" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D371" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="E371" t="s">
         <v>65</v>
@@ -9130,10 +9108,10 @@
         <v>23</v>
       </c>
       <c r="B372" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D372" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="E372" t="s">
         <v>65</v>
@@ -9148,13 +9126,13 @@
         <v>23</v>
       </c>
       <c r="B373" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D373" t="s">
-        <v>163</v>
+        <v>272</v>
       </c>
       <c r="E373" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F373" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9166,13 +9144,13 @@
         <v>23</v>
       </c>
       <c r="B374" t="s">
-        <v>291</v>
+        <v>340</v>
       </c>
       <c r="D374" t="s">
-        <v>67</v>
+        <v>345</v>
       </c>
       <c r="E374" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F374" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9184,13 +9162,13 @@
         <v>23</v>
       </c>
       <c r="B375" t="s">
-        <v>291</v>
+        <v>340</v>
       </c>
       <c r="D375" t="s">
-        <v>292</v>
+        <v>346</v>
       </c>
       <c r="E375" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F375" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9202,13 +9180,13 @@
         <v>23</v>
       </c>
       <c r="B376" t="s">
-        <v>291</v>
+        <v>340</v>
       </c>
       <c r="D376" t="s">
-        <v>354</v>
+        <v>288</v>
       </c>
       <c r="E376" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F376" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9220,10 +9198,10 @@
         <v>23</v>
       </c>
       <c r="B377" t="s">
-        <v>291</v>
+        <v>347</v>
       </c>
       <c r="D377" t="s">
-        <v>293</v>
+        <v>329</v>
       </c>
       <c r="E377" t="s">
         <v>65</v>
@@ -9238,13 +9216,13 @@
         <v>23</v>
       </c>
       <c r="B378" t="s">
-        <v>291</v>
+        <v>347</v>
       </c>
       <c r="D378" t="s">
-        <v>71</v>
+        <v>317</v>
       </c>
       <c r="E378" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F378" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9256,10 +9234,10 @@
         <v>23</v>
       </c>
       <c r="B379" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="D379" t="s">
-        <v>67</v>
+        <v>327</v>
       </c>
       <c r="E379" t="s">
         <v>65</v>
@@ -9274,10 +9252,10 @@
         <v>23</v>
       </c>
       <c r="B380" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="D380" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
       <c r="E380" t="s">
         <v>65</v>
@@ -9292,10 +9270,10 @@
         <v>23</v>
       </c>
       <c r="B381" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="D381" t="s">
-        <v>356</v>
+        <v>163</v>
       </c>
       <c r="E381" t="s">
         <v>65</v>
@@ -9310,13 +9288,13 @@
         <v>23</v>
       </c>
       <c r="B382" t="s">
-        <v>355</v>
+        <v>285</v>
       </c>
       <c r="D382" t="s">
-        <v>294</v>
+        <v>67</v>
       </c>
       <c r="E382" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F382" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9328,10 +9306,10 @@
         <v>23</v>
       </c>
       <c r="B383" t="s">
-        <v>337</v>
+        <v>285</v>
       </c>
       <c r="D383" t="s">
-        <v>67</v>
+        <v>286</v>
       </c>
       <c r="E383" t="s">
         <v>65</v>
@@ -9346,10 +9324,10 @@
         <v>23</v>
       </c>
       <c r="B384" t="s">
-        <v>337</v>
+        <v>285</v>
       </c>
       <c r="D384" t="s">
-        <v>164</v>
+        <v>348</v>
       </c>
       <c r="E384" t="s">
         <v>65</v>
@@ -9364,10 +9342,10 @@
         <v>23</v>
       </c>
       <c r="B385" t="s">
-        <v>337</v>
+        <v>285</v>
       </c>
       <c r="D385" t="s">
-        <v>324</v>
+        <v>287</v>
       </c>
       <c r="E385" t="s">
         <v>65</v>
@@ -9382,7 +9360,7 @@
         <v>23</v>
       </c>
       <c r="B386" t="s">
-        <v>337</v>
+        <v>285</v>
       </c>
       <c r="D386" t="s">
         <v>71</v>
@@ -9400,13 +9378,13 @@
         <v>23</v>
       </c>
       <c r="B387" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="D387" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E387" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F387" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9415,13 +9393,13 @@
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A388" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B388" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="D388" t="s">
-        <v>67</v>
+        <v>286</v>
       </c>
       <c r="E388" t="s">
         <v>65</v>
@@ -9433,13 +9411,13 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A389" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B389" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="D389" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="E389" t="s">
         <v>65</v>
@@ -9451,16 +9429,16 @@
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A390" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B390" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="D390" t="s">
-        <v>358</v>
+        <v>288</v>
       </c>
       <c r="E390" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F390" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9469,16 +9447,16 @@
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A391" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B391" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="D391" t="s">
-        <v>294</v>
+        <v>67</v>
       </c>
       <c r="E391" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F391" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9487,13 +9465,13 @@
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A392" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B392" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="D392" t="s">
-        <v>347</v>
+        <v>164</v>
       </c>
       <c r="E392" t="s">
         <v>65</v>
@@ -9505,13 +9483,13 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A393" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B393" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="D393" t="s">
-        <v>348</v>
+        <v>318</v>
       </c>
       <c r="E393" t="s">
         <v>65</v>
@@ -9523,16 +9501,16 @@
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A394" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B394" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="D394" t="s">
-        <v>342</v>
+        <v>71</v>
       </c>
       <c r="E394" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F394" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9541,16 +9519,16 @@
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A395" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B395" t="s">
-        <v>346</v>
+        <v>331</v>
       </c>
       <c r="D395" t="s">
-        <v>359</v>
+        <v>71</v>
       </c>
       <c r="E395" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F395" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9559,13 +9537,13 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A396" t="s">
-        <v>24</v>
+        <v>562</v>
       </c>
       <c r="B396" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D396" t="s">
-        <v>360</v>
+        <v>67</v>
       </c>
       <c r="E396" t="s">
         <v>65</v>
@@ -9577,13 +9555,13 @@
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A397" t="s">
-        <v>24</v>
+        <v>562</v>
       </c>
       <c r="B397" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D397" t="s">
-        <v>349</v>
+        <v>563</v>
       </c>
       <c r="E397" t="s">
         <v>65</v>
@@ -9595,13 +9573,13 @@
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A398" t="s">
-        <v>24</v>
+        <v>562</v>
       </c>
       <c r="B398" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D398" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="E398" t="s">
         <v>65</v>
@@ -9613,13 +9591,13 @@
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A399" t="s">
-        <v>24</v>
+        <v>562</v>
       </c>
       <c r="B399" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="D399" t="s">
-        <v>351</v>
+        <v>288</v>
       </c>
       <c r="E399" t="s">
         <v>46</v>
@@ -9631,16 +9609,16 @@
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A400" t="s">
-        <v>24</v>
+        <v>562</v>
       </c>
       <c r="B400" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D400" t="s">
-        <v>352</v>
+        <v>341</v>
       </c>
       <c r="E400" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F400" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9649,13 +9627,13 @@
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A401" t="s">
-        <v>24</v>
+        <v>562</v>
       </c>
       <c r="B401" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D401" t="s">
-        <v>323</v>
+        <v>342</v>
       </c>
       <c r="E401" t="s">
         <v>65</v>
@@ -9667,10 +9645,10 @@
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A402" t="s">
-        <v>24</v>
+        <v>562</v>
       </c>
       <c r="B402" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="D402" t="s">
         <v>336</v>
@@ -9685,13 +9663,13 @@
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A403" t="s">
-        <v>24</v>
+        <v>562</v>
       </c>
       <c r="B403" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="D403" t="s">
-        <v>67</v>
+        <v>352</v>
       </c>
       <c r="E403" t="s">
         <v>65</v>
@@ -9703,13 +9681,13 @@
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A404" t="s">
-        <v>24</v>
+        <v>562</v>
       </c>
       <c r="B404" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="D404" t="s">
-        <v>106</v>
+        <v>353</v>
       </c>
       <c r="E404" t="s">
         <v>65</v>
@@ -9721,16 +9699,16 @@
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A405" t="s">
-        <v>24</v>
+        <v>562</v>
       </c>
       <c r="B405" t="s">
-        <v>362</v>
+        <v>340</v>
       </c>
       <c r="D405" t="s">
-        <v>71</v>
+        <v>343</v>
       </c>
       <c r="E405" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F405" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9739,13 +9717,13 @@
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A406" t="s">
-        <v>25</v>
+        <v>562</v>
       </c>
       <c r="B406" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="D406" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="E406" t="s">
         <v>65</v>
@@ -9757,16 +9735,16 @@
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A407" t="s">
-        <v>25</v>
+        <v>562</v>
       </c>
       <c r="B407" t="s">
-        <v>363</v>
+        <v>340</v>
       </c>
       <c r="D407" t="s">
-        <v>365</v>
+        <v>345</v>
       </c>
       <c r="E407" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F407" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9775,16 +9753,16 @@
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A408" t="s">
-        <v>25</v>
+        <v>562</v>
       </c>
       <c r="B408" t="s">
-        <v>366</v>
+        <v>340</v>
       </c>
       <c r="D408" t="s">
-        <v>367</v>
+        <v>346</v>
       </c>
       <c r="E408" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F408" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9793,13 +9771,13 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A409" t="s">
-        <v>25</v>
+        <v>562</v>
       </c>
       <c r="B409" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="D409" t="s">
-        <v>368</v>
+        <v>317</v>
       </c>
       <c r="E409" t="s">
         <v>65</v>
@@ -9811,13 +9789,13 @@
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A410" t="s">
-        <v>25</v>
+        <v>562</v>
       </c>
       <c r="B410" t="s">
-        <v>369</v>
+        <v>347</v>
       </c>
       <c r="D410" t="s">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="E410" t="s">
         <v>65</v>
@@ -9829,13 +9807,13 @@
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A411" t="s">
-        <v>25</v>
+        <v>562</v>
       </c>
       <c r="B411" t="s">
-        <v>369</v>
+        <v>355</v>
       </c>
       <c r="D411" t="s">
-        <v>371</v>
+        <v>67</v>
       </c>
       <c r="E411" t="s">
         <v>65</v>
@@ -9847,13 +9825,13 @@
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A412" t="s">
-        <v>25</v>
+        <v>562</v>
       </c>
       <c r="B412" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="D412" t="s">
-        <v>373</v>
+        <v>106</v>
       </c>
       <c r="E412" t="s">
         <v>65</v>
@@ -9865,16 +9843,16 @@
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A413" t="s">
-        <v>25</v>
+        <v>562</v>
       </c>
       <c r="B413" t="s">
-        <v>372</v>
+        <v>355</v>
       </c>
       <c r="D413" t="s">
-        <v>374</v>
+        <v>71</v>
       </c>
       <c r="E413" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F413" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -9886,10 +9864,10 @@
         <v>25</v>
       </c>
       <c r="B414" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="D414" t="s">
-        <v>375</v>
+        <v>357</v>
       </c>
       <c r="E414" t="s">
         <v>65</v>
@@ -9904,10 +9882,10 @@
         <v>25</v>
       </c>
       <c r="B415" t="s">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="D415" t="s">
-        <v>376</v>
+        <v>358</v>
       </c>
       <c r="E415" t="s">
         <v>65</v>
@@ -9922,10 +9900,10 @@
         <v>25</v>
       </c>
       <c r="B416" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="D416" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="E416" t="s">
         <v>65</v>
@@ -9940,10 +9918,10 @@
         <v>25</v>
       </c>
       <c r="B417" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="D417" t="s">
-        <v>378</v>
+        <v>361</v>
       </c>
       <c r="E417" t="s">
         <v>65</v>
@@ -9958,10 +9936,10 @@
         <v>25</v>
       </c>
       <c r="B418" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D418" t="s">
-        <v>379</v>
+        <v>363</v>
       </c>
       <c r="E418" t="s">
         <v>65</v>
@@ -9976,10 +9954,10 @@
         <v>25</v>
       </c>
       <c r="B419" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D419" t="s">
-        <v>380</v>
+        <v>364</v>
       </c>
       <c r="E419" t="s">
         <v>65</v>
@@ -9994,13 +9972,13 @@
         <v>25</v>
       </c>
       <c r="B420" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="D420" t="s">
-        <v>381</v>
+        <v>366</v>
       </c>
       <c r="E420" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F420" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10012,10 +9990,10 @@
         <v>25</v>
       </c>
       <c r="B421" t="s">
-        <v>372</v>
+        <v>365</v>
       </c>
       <c r="D421" t="s">
-        <v>382</v>
+        <v>367</v>
       </c>
       <c r="E421" t="s">
         <v>65</v>
@@ -10030,10 +10008,10 @@
         <v>25</v>
       </c>
       <c r="B422" t="s">
-        <v>43</v>
+        <v>365</v>
       </c>
       <c r="D422" t="s">
-        <v>271</v>
+        <v>368</v>
       </c>
       <c r="E422" t="s">
         <v>65</v>
@@ -10048,10 +10026,10 @@
         <v>25</v>
       </c>
       <c r="B423" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="D423" t="s">
-        <v>384</v>
+        <v>369</v>
       </c>
       <c r="E423" t="s">
         <v>65</v>
@@ -10066,10 +10044,10 @@
         <v>25</v>
       </c>
       <c r="B424" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="D424" t="s">
-        <v>385</v>
+        <v>370</v>
       </c>
       <c r="E424" t="s">
         <v>65</v>
@@ -10084,10 +10062,10 @@
         <v>25</v>
       </c>
       <c r="B425" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="D425" t="s">
-        <v>67</v>
+        <v>371</v>
       </c>
       <c r="E425" t="s">
         <v>65</v>
@@ -10102,10 +10080,10 @@
         <v>25</v>
       </c>
       <c r="B426" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="D426" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="E426" t="s">
         <v>65</v>
@@ -10120,10 +10098,10 @@
         <v>25</v>
       </c>
       <c r="B427" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="D427" t="s">
-        <v>388</v>
+        <v>373</v>
       </c>
       <c r="E427" t="s">
         <v>65</v>
@@ -10138,13 +10116,13 @@
         <v>25</v>
       </c>
       <c r="B428" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="D428" t="s">
-        <v>202</v>
+        <v>374</v>
       </c>
       <c r="E428" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F428" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10156,13 +10134,13 @@
         <v>25</v>
       </c>
       <c r="B429" t="s">
-        <v>386</v>
+        <v>365</v>
       </c>
       <c r="D429" t="s">
-        <v>272</v>
+        <v>375</v>
       </c>
       <c r="E429" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F429" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10174,10 +10152,10 @@
         <v>25</v>
       </c>
       <c r="B430" t="s">
-        <v>389</v>
+        <v>43</v>
       </c>
       <c r="D430" t="s">
-        <v>206</v>
+        <v>271</v>
       </c>
       <c r="E430" t="s">
         <v>65</v>
@@ -10192,10 +10170,10 @@
         <v>25</v>
       </c>
       <c r="B431" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="D431" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="E431" t="s">
         <v>65</v>
@@ -10210,13 +10188,13 @@
         <v>25</v>
       </c>
       <c r="B432" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="D432" t="s">
-        <v>71</v>
+        <v>378</v>
       </c>
       <c r="E432" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F432" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10225,7 +10203,10 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A433" t="s">
-        <v>26</v>
+        <v>25</v>
+      </c>
+      <c r="B433" t="s">
+        <v>379</v>
       </c>
       <c r="D433" t="s">
         <v>67</v>
@@ -10240,13 +10221,13 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A434" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B434" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="D434" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="E434" t="s">
         <v>65</v>
@@ -10258,16 +10239,16 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A435" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B435" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="D435" t="s">
-        <v>393</v>
+        <v>381</v>
       </c>
       <c r="E435" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F435" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10276,13 +10257,13 @@
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A436" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B436" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="D436" t="s">
-        <v>394</v>
+        <v>202</v>
       </c>
       <c r="E436" t="s">
         <v>65</v>
@@ -10294,16 +10275,16 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A437" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B437" t="s">
-        <v>391</v>
+        <v>379</v>
       </c>
       <c r="D437" t="s">
-        <v>395</v>
+        <v>272</v>
       </c>
       <c r="E437" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F437" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10312,13 +10293,13 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A438" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B438" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="D438" t="s">
-        <v>396</v>
+        <v>206</v>
       </c>
       <c r="E438" t="s">
         <v>65</v>
@@ -10330,13 +10311,13 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A439" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B439" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="D439" t="s">
-        <v>397</v>
+        <v>383</v>
       </c>
       <c r="E439" t="s">
         <v>65</v>
@@ -10348,16 +10329,16 @@
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A440" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B440" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="D440" t="s">
-        <v>398</v>
+        <v>71</v>
       </c>
       <c r="E440" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F440" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10368,11 +10349,8 @@
       <c r="A441" t="s">
         <v>26</v>
       </c>
-      <c r="B441" t="s">
-        <v>391</v>
-      </c>
       <c r="D441" t="s">
-        <v>399</v>
+        <v>67</v>
       </c>
       <c r="E441" t="s">
         <v>65</v>
@@ -10387,13 +10365,13 @@
         <v>26</v>
       </c>
       <c r="B442" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="D442" t="s">
-        <v>400</v>
+        <v>385</v>
       </c>
       <c r="E442" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F442" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10405,13 +10383,13 @@
         <v>26</v>
       </c>
       <c r="B443" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="D443" t="s">
-        <v>401</v>
+        <v>386</v>
       </c>
       <c r="E443" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F443" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10423,13 +10401,13 @@
         <v>26</v>
       </c>
       <c r="B444" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="D444" t="s">
-        <v>294</v>
+        <v>387</v>
       </c>
       <c r="E444" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F444" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10441,10 +10419,10 @@
         <v>26</v>
       </c>
       <c r="B445" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="D445" t="s">
-        <v>403</v>
+        <v>388</v>
       </c>
       <c r="E445" t="s">
         <v>65</v>
@@ -10459,10 +10437,10 @@
         <v>26</v>
       </c>
       <c r="B446" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="D446" t="s">
-        <v>404</v>
+        <v>389</v>
       </c>
       <c r="E446" t="s">
         <v>65</v>
@@ -10477,10 +10455,10 @@
         <v>26</v>
       </c>
       <c r="B447" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="D447" t="s">
-        <v>405</v>
+        <v>390</v>
       </c>
       <c r="E447" t="s">
         <v>65</v>
@@ -10495,13 +10473,13 @@
         <v>26</v>
       </c>
       <c r="B448" t="s">
-        <v>402</v>
+        <v>384</v>
       </c>
       <c r="D448" t="s">
-        <v>294</v>
+        <v>391</v>
       </c>
       <c r="E448" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F448" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10513,10 +10491,10 @@
         <v>26</v>
       </c>
       <c r="B449" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
       <c r="D449" t="s">
-        <v>407</v>
+        <v>392</v>
       </c>
       <c r="E449" t="s">
         <v>65</v>
@@ -10531,10 +10509,10 @@
         <v>26</v>
       </c>
       <c r="B450" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
       <c r="D450" t="s">
-        <v>408</v>
+        <v>393</v>
       </c>
       <c r="E450" t="s">
         <v>46</v>
@@ -10549,10 +10527,10 @@
         <v>26</v>
       </c>
       <c r="B451" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
       <c r="D451" t="s">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="E451" t="s">
         <v>65</v>
@@ -10567,13 +10545,13 @@
         <v>26</v>
       </c>
       <c r="B452" t="s">
-        <v>406</v>
+        <v>384</v>
       </c>
       <c r="D452" t="s">
-        <v>409</v>
+        <v>288</v>
       </c>
       <c r="E452" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F452" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10585,10 +10563,10 @@
         <v>26</v>
       </c>
       <c r="B453" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="D453" t="s">
-        <v>410</v>
+        <v>396</v>
       </c>
       <c r="E453" t="s">
         <v>65</v>
@@ -10603,13 +10581,13 @@
         <v>26</v>
       </c>
       <c r="B454" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="D454" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="E454" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F454" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10621,13 +10599,13 @@
         <v>26</v>
       </c>
       <c r="B455" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="D455" t="s">
-        <v>71</v>
+        <v>398</v>
       </c>
       <c r="E455" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F455" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10639,13 +10617,13 @@
         <v>26</v>
       </c>
       <c r="B456" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="D456" t="s">
-        <v>67</v>
+        <v>288</v>
       </c>
       <c r="E456" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F456" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10657,10 +10635,10 @@
         <v>26</v>
       </c>
       <c r="B457" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="D457" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="E457" t="s">
         <v>65</v>
@@ -10675,13 +10653,13 @@
         <v>26</v>
       </c>
       <c r="B458" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="D458" t="s">
-        <v>82</v>
+        <v>401</v>
       </c>
       <c r="E458" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F458" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10693,13 +10671,13 @@
         <v>26</v>
       </c>
       <c r="B459" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="D459" t="s">
-        <v>272</v>
+        <v>82</v>
       </c>
       <c r="E459" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F459" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10711,10 +10689,10 @@
         <v>26</v>
       </c>
       <c r="B460" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="D460" t="s">
-        <v>227</v>
+        <v>402</v>
       </c>
       <c r="E460" t="s">
         <v>65</v>
@@ -10729,10 +10707,10 @@
         <v>26</v>
       </c>
       <c r="B461" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="D461" t="s">
-        <v>226</v>
+        <v>403</v>
       </c>
       <c r="E461" t="s">
         <v>65</v>
@@ -10747,13 +10725,13 @@
         <v>26</v>
       </c>
       <c r="B462" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="D462" t="s">
-        <v>413</v>
+        <v>401</v>
       </c>
       <c r="E462" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F462" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10765,13 +10743,13 @@
         <v>26</v>
       </c>
       <c r="B463" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="D463" t="s">
-        <v>414</v>
+        <v>71</v>
       </c>
       <c r="E463" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F463" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10783,10 +10761,10 @@
         <v>26</v>
       </c>
       <c r="B464" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D464" t="s">
-        <v>326</v>
+        <v>67</v>
       </c>
       <c r="E464" t="s">
         <v>65</v>
@@ -10801,10 +10779,10 @@
         <v>26</v>
       </c>
       <c r="B465" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D465" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="E465" t="s">
         <v>65</v>
@@ -10819,10 +10797,10 @@
         <v>26</v>
       </c>
       <c r="B466" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D466" t="s">
-        <v>416</v>
+        <v>82</v>
       </c>
       <c r="E466" t="s">
         <v>65</v>
@@ -10837,13 +10815,13 @@
         <v>26</v>
       </c>
       <c r="B467" t="s">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="D467" t="s">
-        <v>417</v>
+        <v>272</v>
       </c>
       <c r="E467" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F467" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10855,10 +10833,10 @@
         <v>26</v>
       </c>
       <c r="B468" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="D468" t="s">
-        <v>419</v>
+        <v>227</v>
       </c>
       <c r="E468" t="s">
         <v>65</v>
@@ -10873,10 +10851,10 @@
         <v>26</v>
       </c>
       <c r="B469" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="D469" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E469" t="s">
         <v>65</v>
@@ -10891,10 +10869,10 @@
         <v>26</v>
       </c>
       <c r="B470" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="D470" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="E470" t="s">
         <v>65</v>
@@ -10909,10 +10887,10 @@
         <v>26</v>
       </c>
       <c r="B471" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="D471" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="E471" t="s">
         <v>65</v>
@@ -10927,10 +10905,10 @@
         <v>26</v>
       </c>
       <c r="B472" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="D472" t="s">
-        <v>422</v>
+        <v>320</v>
       </c>
       <c r="E472" t="s">
         <v>65</v>
@@ -10945,10 +10923,10 @@
         <v>26</v>
       </c>
       <c r="B473" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="D473" t="s">
-        <v>82</v>
+        <v>408</v>
       </c>
       <c r="E473" t="s">
         <v>65</v>
@@ -10963,13 +10941,13 @@
         <v>26</v>
       </c>
       <c r="B474" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="D474" t="s">
-        <v>71</v>
+        <v>409</v>
       </c>
       <c r="E474" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F474" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10981,13 +10959,13 @@
         <v>26</v>
       </c>
       <c r="B475" t="s">
-        <v>418</v>
+        <v>404</v>
       </c>
       <c r="D475" t="s">
-        <v>71</v>
+        <v>410</v>
       </c>
       <c r="E475" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="F475" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -10996,10 +10974,13 @@
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A476" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="B476" t="s">
+        <v>411</v>
       </c>
       <c r="D476" t="s">
-        <v>423</v>
+        <v>412</v>
       </c>
       <c r="E476" t="s">
         <v>65</v>
@@ -11011,10 +10992,13 @@
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A477" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="B477" t="s">
+        <v>411</v>
       </c>
       <c r="D477" t="s">
-        <v>424</v>
+        <v>228</v>
       </c>
       <c r="E477" t="s">
         <v>65</v>
@@ -11026,10 +11010,13 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A478" t="s">
-        <v>27</v>
+        <v>26</v>
+      </c>
+      <c r="B478" t="s">
+        <v>411</v>
       </c>
       <c r="D478" t="s">
-        <v>425</v>
+        <v>413</v>
       </c>
       <c r="E478" t="s">
         <v>65</v>
@@ -11041,13 +11028,13 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A479" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B479" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="D479" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="E479" t="s">
         <v>65</v>
@@ -11059,13 +11046,13 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A480" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B480" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="D480" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="E480" t="s">
         <v>65</v>
@@ -11077,13 +11064,13 @@
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A481" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B481" t="s">
-        <v>426</v>
+        <v>411</v>
       </c>
       <c r="D481" t="s">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="E481" t="s">
         <v>65</v>
@@ -11095,16 +11082,16 @@
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A482" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B482" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="D482" t="s">
-        <v>431</v>
+        <v>71</v>
       </c>
       <c r="E482" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="F482" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
@@ -11113,10 +11100,10 @@
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A483" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B483" t="s">
-        <v>430</v>
+        <v>411</v>
       </c>
       <c r="D483" t="s">
         <v>71</v>
@@ -11134,10 +11121,10 @@
         <v>28</v>
       </c>
       <c r="B484" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="D484" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="E484" t="s">
         <v>65</v>
@@ -11152,10 +11139,10 @@
         <v>28</v>
       </c>
       <c r="B485" t="s">
-        <v>432</v>
+        <v>416</v>
       </c>
       <c r="D485" t="s">
-        <v>434</v>
+        <v>418</v>
       </c>
       <c r="E485" t="s">
         <v>65</v>
@@ -11170,10 +11157,10 @@
         <v>28</v>
       </c>
       <c r="B486" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
       <c r="D486" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="E486" t="s">
         <v>65</v>
@@ -11188,10 +11175,10 @@
         <v>28</v>
       </c>
       <c r="B487" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="D487" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="E487" t="s">
         <v>65</v>
@@ -11206,10 +11193,10 @@
         <v>28</v>
       </c>
       <c r="B488" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
       <c r="D488" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
       <c r="E488" t="s">
         <v>65</v>
@@ -11224,10 +11211,10 @@
         <v>28</v>
       </c>
       <c r="B489" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="D489" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E489" t="s">
         <v>65</v>
@@ -11242,10 +11229,10 @@
         <v>28</v>
       </c>
       <c r="B490" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="D490" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="E490" t="s">
         <v>65</v>
@@ -11260,10 +11247,10 @@
         <v>28</v>
       </c>
       <c r="B491" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="D491" t="s">
-        <v>443</v>
+        <v>427</v>
       </c>
       <c r="E491" t="s">
         <v>65</v>
@@ -11278,10 +11265,10 @@
         <v>28</v>
       </c>
       <c r="B492" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="D492" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="E492" t="s">
         <v>65</v>
@@ -11296,7 +11283,7 @@
         <v>28</v>
       </c>
       <c r="B493" t="s">
-        <v>386</v>
+        <v>379</v>
       </c>
       <c r="D493" t="s">
         <v>84</v>
@@ -11314,7 +11301,7 @@
         <v>28</v>
       </c>
       <c r="B494" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="D494" t="s">
         <v>67</v>
@@ -11332,10 +11319,10 @@
         <v>28</v>
       </c>
       <c r="B495" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="D495" t="s">
-        <v>447</v>
+        <v>431</v>
       </c>
       <c r="E495" t="s">
         <v>65</v>
@@ -11350,10 +11337,10 @@
         <v>28</v>
       </c>
       <c r="B496" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="D496" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="E496" t="s">
         <v>65</v>
@@ -11368,7 +11355,7 @@
         <v>28</v>
       </c>
       <c r="B497" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="D497" t="s">
         <v>67</v>
@@ -11386,10 +11373,10 @@
         <v>28</v>
       </c>
       <c r="B498" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="D498" t="s">
-        <v>445</v>
+        <v>429</v>
       </c>
       <c r="E498" t="s">
         <v>65</v>
@@ -11404,10 +11391,10 @@
         <v>28</v>
       </c>
       <c r="B499" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="D499" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="E499" t="s">
         <v>65</v>
@@ -11422,7 +11409,7 @@
         <v>28</v>
       </c>
       <c r="B500" t="s">
-        <v>449</v>
+        <v>433</v>
       </c>
       <c r="D500" t="s">
         <v>71</v>
@@ -11440,7 +11427,7 @@
         <v>29</v>
       </c>
       <c r="D501" t="s">
-        <v>451</v>
+        <v>435</v>
       </c>
       <c r="E501" t="s">
         <v>65</v>
@@ -11455,7 +11442,7 @@
         <v>29</v>
       </c>
       <c r="B502" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="D502" t="s">
         <v>71</v>
@@ -11473,10 +11460,10 @@
         <v>30</v>
       </c>
       <c r="B503" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="D503" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="E503" t="s">
         <v>65</v>
@@ -11491,10 +11478,10 @@
         <v>30</v>
       </c>
       <c r="B504" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="D504" t="s">
-        <v>455</v>
+        <v>439</v>
       </c>
       <c r="E504" t="s">
         <v>65</v>
@@ -11509,10 +11496,10 @@
         <v>30</v>
       </c>
       <c r="B505" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="D505" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="E505" t="s">
         <v>65</v>
@@ -11527,10 +11514,10 @@
         <v>30</v>
       </c>
       <c r="B506" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="D506" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="E506" t="s">
         <v>65</v>
@@ -11545,10 +11532,10 @@
         <v>30</v>
       </c>
       <c r="B507" t="s">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="D507" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="E507" t="s">
         <v>65</v>
@@ -11563,7 +11550,7 @@
         <v>30</v>
       </c>
       <c r="B508" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D508" t="s">
         <v>67</v>
@@ -11581,10 +11568,10 @@
         <v>30</v>
       </c>
       <c r="B509" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D509" t="s">
-        <v>460</v>
+        <v>444</v>
       </c>
       <c r="E509" t="s">
         <v>65</v>
@@ -11599,10 +11586,10 @@
         <v>30</v>
       </c>
       <c r="B510" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D510" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="E510" t="s">
         <v>65</v>
@@ -11617,10 +11604,10 @@
         <v>30</v>
       </c>
       <c r="B511" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D511" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="E511" t="s">
         <v>65</v>
@@ -11635,10 +11622,10 @@
         <v>30</v>
       </c>
       <c r="B512" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D512" t="s">
-        <v>463</v>
+        <v>447</v>
       </c>
       <c r="E512" t="s">
         <v>65</v>
@@ -11653,10 +11640,10 @@
         <v>30</v>
       </c>
       <c r="B513" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D513" t="s">
-        <v>464</v>
+        <v>448</v>
       </c>
       <c r="E513" t="s">
         <v>46</v>
@@ -11671,10 +11658,10 @@
         <v>30</v>
       </c>
       <c r="B514" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D514" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="E514" t="s">
         <v>65</v>
@@ -11689,10 +11676,10 @@
         <v>30</v>
       </c>
       <c r="B515" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D515" t="s">
-        <v>466</v>
+        <v>450</v>
       </c>
       <c r="E515" t="s">
         <v>65</v>
@@ -11707,10 +11694,10 @@
         <v>30</v>
       </c>
       <c r="B516" t="s">
-        <v>459</v>
+        <v>443</v>
       </c>
       <c r="D516" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E516" t="s">
         <v>46</v>
@@ -11725,10 +11712,10 @@
         <v>30</v>
       </c>
       <c r="B517" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D517" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="E517" t="s">
         <v>65</v>
@@ -11743,10 +11730,10 @@
         <v>30</v>
       </c>
       <c r="B518" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D518" t="s">
-        <v>469</v>
+        <v>453</v>
       </c>
       <c r="E518" t="s">
         <v>65</v>
@@ -11761,10 +11748,10 @@
         <v>30</v>
       </c>
       <c r="B519" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D519" t="s">
-        <v>470</v>
+        <v>454</v>
       </c>
       <c r="E519" t="s">
         <v>65</v>
@@ -11779,10 +11766,10 @@
         <v>30</v>
       </c>
       <c r="B520" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D520" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="E520" t="s">
         <v>65</v>
@@ -11797,10 +11784,10 @@
         <v>30</v>
       </c>
       <c r="B521" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D521" t="s">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="E521" t="s">
         <v>65</v>
@@ -11815,10 +11802,10 @@
         <v>30</v>
       </c>
       <c r="B522" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D522" t="s">
-        <v>473</v>
+        <v>457</v>
       </c>
       <c r="E522" t="s">
         <v>65</v>
@@ -11833,10 +11820,10 @@
         <v>30</v>
       </c>
       <c r="B523" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D523" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="E523" t="s">
         <v>65</v>
@@ -11851,10 +11838,10 @@
         <v>30</v>
       </c>
       <c r="B524" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D524" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="E524" t="s">
         <v>46</v>
@@ -11869,7 +11856,7 @@
         <v>30</v>
       </c>
       <c r="B525" t="s">
-        <v>467</v>
+        <v>451</v>
       </c>
       <c r="D525" t="s">
         <v>71</v>
@@ -11887,10 +11874,10 @@
         <v>31</v>
       </c>
       <c r="B526" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="D526" t="s">
-        <v>476</v>
+        <v>564</v>
       </c>
       <c r="E526" t="s">
         <v>65</v>
@@ -11905,10 +11892,10 @@
         <v>31</v>
       </c>
       <c r="B527" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="D527" t="s">
-        <v>477</v>
+        <v>565</v>
       </c>
       <c r="E527" t="s">
         <v>65</v>
@@ -11923,10 +11910,10 @@
         <v>31</v>
       </c>
       <c r="B528" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="D528" t="s">
-        <v>478</v>
+        <v>566</v>
       </c>
       <c r="E528" t="s">
         <v>65</v>
@@ -11941,7 +11928,7 @@
         <v>31</v>
       </c>
       <c r="B529" t="s">
-        <v>475</v>
+        <v>459</v>
       </c>
       <c r="D529" t="s">
         <v>75</v>
@@ -11959,10 +11946,10 @@
         <v>31</v>
       </c>
       <c r="B530" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="D530" t="s">
-        <v>480</v>
+        <v>461</v>
       </c>
       <c r="E530" t="s">
         <v>46</v>
@@ -11977,10 +11964,10 @@
         <v>31</v>
       </c>
       <c r="B531" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="D531" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="E531" t="s">
         <v>46</v>
@@ -11995,10 +11982,10 @@
         <v>31</v>
       </c>
       <c r="B532" t="s">
-        <v>479</v>
+        <v>460</v>
       </c>
       <c r="D532" t="s">
-        <v>482</v>
+        <v>463</v>
       </c>
       <c r="E532" t="s">
         <v>46</v>
@@ -12013,10 +12000,10 @@
         <v>31</v>
       </c>
       <c r="B533" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="D533" t="s">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="E533" t="s">
         <v>65</v>
@@ -12031,7 +12018,7 @@
         <v>31</v>
       </c>
       <c r="B534" t="s">
-        <v>483</v>
+        <v>464</v>
       </c>
       <c r="D534" t="s">
         <v>75</v>
@@ -12049,7 +12036,7 @@
         <v>31</v>
       </c>
       <c r="B535" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="D535" t="s">
         <v>275</v>
@@ -12067,10 +12054,10 @@
         <v>31</v>
       </c>
       <c r="B536" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="D536" t="s">
-        <v>486</v>
+        <v>467</v>
       </c>
       <c r="E536" t="s">
         <v>65</v>
@@ -12085,10 +12072,10 @@
         <v>31</v>
       </c>
       <c r="B537" t="s">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="D537" t="s">
-        <v>487</v>
+        <v>567</v>
       </c>
       <c r="E537" t="s">
         <v>65</v>
@@ -12103,10 +12090,10 @@
         <v>31</v>
       </c>
       <c r="B538" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="D538" t="s">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="E538" t="s">
         <v>65</v>
@@ -12121,10 +12108,10 @@
         <v>31</v>
       </c>
       <c r="B539" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="D539" t="s">
-        <v>490</v>
+        <v>470</v>
       </c>
       <c r="E539" t="s">
         <v>65</v>
@@ -12139,10 +12126,10 @@
         <v>31</v>
       </c>
       <c r="B540" t="s">
-        <v>488</v>
+        <v>468</v>
       </c>
       <c r="D540" t="s">
-        <v>491</v>
+        <v>471</v>
       </c>
       <c r="E540" t="s">
         <v>65</v>
@@ -12157,10 +12144,10 @@
         <v>31</v>
       </c>
       <c r="B541" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="D541" t="s">
-        <v>370</v>
+        <v>363</v>
       </c>
       <c r="E541" t="s">
         <v>65</v>
@@ -12175,10 +12162,10 @@
         <v>31</v>
       </c>
       <c r="B542" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="D542" t="s">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="E542" t="s">
         <v>65</v>
@@ -12193,10 +12180,10 @@
         <v>31</v>
       </c>
       <c r="B543" t="s">
-        <v>492</v>
+        <v>472</v>
       </c>
       <c r="D543" t="s">
-        <v>494</v>
+        <v>474</v>
       </c>
       <c r="E543" t="s">
         <v>46</v>
@@ -12211,7 +12198,7 @@
         <v>31</v>
       </c>
       <c r="B544" t="s">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="D544" t="s">
         <v>67</v>
@@ -12229,10 +12216,10 @@
         <v>31</v>
       </c>
       <c r="B545" t="s">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="D545" t="s">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="E545" t="s">
         <v>65</v>
@@ -12247,10 +12234,10 @@
         <v>31</v>
       </c>
       <c r="B546" t="s">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="D546" t="s">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="E546" t="s">
         <v>65</v>
@@ -12265,7 +12252,7 @@
         <v>31</v>
       </c>
       <c r="B547" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="D547" t="s">
         <v>67</v>
@@ -12283,10 +12270,10 @@
         <v>31</v>
       </c>
       <c r="B548" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="D548" t="s">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="E548" t="s">
         <v>65</v>
@@ -12301,10 +12288,10 @@
         <v>31</v>
       </c>
       <c r="B549" t="s">
-        <v>498</v>
+        <v>478</v>
       </c>
       <c r="D549" t="s">
-        <v>497</v>
+        <v>477</v>
       </c>
       <c r="E549" t="s">
         <v>65</v>
@@ -12319,7 +12306,7 @@
         <v>31</v>
       </c>
       <c r="B550" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="D550" t="s">
         <v>67</v>
@@ -12337,10 +12324,10 @@
         <v>31</v>
       </c>
       <c r="B551" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="D551" t="s">
-        <v>500</v>
+        <v>480</v>
       </c>
       <c r="E551" t="s">
         <v>65</v>
@@ -12355,10 +12342,10 @@
         <v>31</v>
       </c>
       <c r="B552" t="s">
-        <v>499</v>
+        <v>479</v>
       </c>
       <c r="D552" t="s">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="E552" t="s">
         <v>65</v>
@@ -12373,13 +12360,13 @@
         <v>31</v>
       </c>
       <c r="B553" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="C553" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="D553" t="s">
-        <v>504</v>
+        <v>484</v>
       </c>
       <c r="E553" t="s">
         <v>65</v>
@@ -12394,13 +12381,13 @@
         <v>31</v>
       </c>
       <c r="B554" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="C554" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="D554" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="E554" t="s">
         <v>65</v>
@@ -12415,13 +12402,13 @@
         <v>31</v>
       </c>
       <c r="B555" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="C555" t="s">
-        <v>503</v>
+        <v>483</v>
       </c>
       <c r="D555" t="s">
-        <v>506</v>
+        <v>486</v>
       </c>
       <c r="E555" t="s">
         <v>65</v>
@@ -12436,13 +12423,13 @@
         <v>31</v>
       </c>
       <c r="B556" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="C556" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="D556" t="s">
-        <v>504</v>
+        <v>484</v>
       </c>
       <c r="E556" t="s">
         <v>65</v>
@@ -12457,13 +12444,13 @@
         <v>31</v>
       </c>
       <c r="B557" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="C557" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="D557" t="s">
-        <v>505</v>
+        <v>485</v>
       </c>
       <c r="E557" t="s">
         <v>65</v>
@@ -12478,13 +12465,13 @@
         <v>31</v>
       </c>
       <c r="B558" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="C558" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="D558" t="s">
-        <v>506</v>
+        <v>486</v>
       </c>
       <c r="E558" t="s">
         <v>65</v>
@@ -12499,10 +12486,10 @@
         <v>31</v>
       </c>
       <c r="B559" t="s">
-        <v>502</v>
+        <v>482</v>
       </c>
       <c r="C559" t="s">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="D559" t="s">
         <v>71</v>
@@ -12535,10 +12522,10 @@
         <v>32</v>
       </c>
       <c r="B561" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="D561" t="s">
-        <v>509</v>
+        <v>489</v>
       </c>
       <c r="E561" t="s">
         <v>65</v>
@@ -12553,10 +12540,10 @@
         <v>32</v>
       </c>
       <c r="B562" t="s">
-        <v>508</v>
+        <v>488</v>
       </c>
       <c r="D562" t="s">
-        <v>510</v>
+        <v>490</v>
       </c>
       <c r="E562" t="s">
         <v>65</v>
@@ -12571,10 +12558,10 @@
         <v>32</v>
       </c>
       <c r="B563" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="D563" t="s">
-        <v>512</v>
+        <v>492</v>
       </c>
       <c r="E563" t="s">
         <v>65</v>
@@ -12589,10 +12576,10 @@
         <v>32</v>
       </c>
       <c r="B564" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="D564" t="s">
-        <v>513</v>
+        <v>493</v>
       </c>
       <c r="E564" t="s">
         <v>65</v>
@@ -12607,7 +12594,7 @@
         <v>32</v>
       </c>
       <c r="B565" t="s">
-        <v>511</v>
+        <v>491</v>
       </c>
       <c r="D565" t="s">
         <v>82</v>
@@ -12625,7 +12612,7 @@
         <v>32</v>
       </c>
       <c r="B566" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="D566" t="s">
         <v>67</v>
@@ -12643,7 +12630,7 @@
         <v>32</v>
       </c>
       <c r="B567" t="s">
-        <v>514</v>
+        <v>494</v>
       </c>
       <c r="D567" t="s">
         <v>106</v>
@@ -12661,7 +12648,7 @@
         <v>32</v>
       </c>
       <c r="B568" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="D568" t="s">
         <v>67</v>
@@ -12679,7 +12666,7 @@
         <v>32</v>
       </c>
       <c r="B569" t="s">
-        <v>515</v>
+        <v>495</v>
       </c>
       <c r="D569" t="s">
         <v>106</v>
@@ -12697,10 +12684,10 @@
         <v>32</v>
       </c>
       <c r="B570" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="D570" t="s">
-        <v>517</v>
+        <v>497</v>
       </c>
       <c r="E570" t="s">
         <v>46</v>
@@ -12715,10 +12702,10 @@
         <v>32</v>
       </c>
       <c r="B571" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="D571" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="E571" t="s">
         <v>46</v>
@@ -12733,10 +12720,10 @@
         <v>32</v>
       </c>
       <c r="B572" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="D572" t="s">
-        <v>519</v>
+        <v>499</v>
       </c>
       <c r="E572" t="s">
         <v>46</v>
@@ -12751,7 +12738,7 @@
         <v>32</v>
       </c>
       <c r="B573" t="s">
-        <v>516</v>
+        <v>496</v>
       </c>
       <c r="D573" t="s">
         <v>71</v>
@@ -12769,10 +12756,10 @@
         <v>33</v>
       </c>
       <c r="B574" t="s">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="D574" t="s">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="E574" t="s">
         <v>46</v>
@@ -12787,7 +12774,7 @@
         <v>33</v>
       </c>
       <c r="B575" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="D575" t="s">
         <v>85</v>
@@ -12805,7 +12792,7 @@
         <v>33</v>
       </c>
       <c r="B576" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="D576" t="s">
         <v>84</v>
@@ -12823,7 +12810,7 @@
         <v>33</v>
       </c>
       <c r="B577" t="s">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="D577" t="s">
         <v>71</v>
@@ -12895,7 +12882,7 @@
         <v>34</v>
       </c>
       <c r="B581" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="D581" t="s">
         <v>106</v>
@@ -12913,7 +12900,7 @@
         <v>34</v>
       </c>
       <c r="B582" t="s">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="D582" t="s">
         <v>107</v>
@@ -12931,7 +12918,7 @@
         <v>34</v>
       </c>
       <c r="B583" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="D583" t="s">
         <v>106</v>
@@ -12949,7 +12936,7 @@
         <v>34</v>
       </c>
       <c r="B584" t="s">
-        <v>524</v>
+        <v>504</v>
       </c>
       <c r="D584" t="s">
         <v>107</v>
@@ -12967,7 +12954,7 @@
         <v>34</v>
       </c>
       <c r="B585" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="D585" t="s">
         <v>106</v>
@@ -12985,7 +12972,7 @@
         <v>34</v>
       </c>
       <c r="B586" t="s">
-        <v>525</v>
+        <v>505</v>
       </c>
       <c r="D586" t="s">
         <v>107</v>
@@ -13006,7 +12993,7 @@
         <v>43</v>
       </c>
       <c r="D587" t="s">
-        <v>526</v>
+        <v>506</v>
       </c>
       <c r="E587" t="s">
         <v>65</v>
@@ -13024,7 +13011,7 @@
         <v>43</v>
       </c>
       <c r="D588" t="s">
-        <v>527</v>
+        <v>507</v>
       </c>
       <c r="E588" t="s">
         <v>65</v>
@@ -13042,7 +13029,7 @@
         <v>43</v>
       </c>
       <c r="D589" t="s">
-        <v>528</v>
+        <v>508</v>
       </c>
       <c r="E589" t="s">
         <v>46</v>
@@ -13075,7 +13062,7 @@
         <v>35</v>
       </c>
       <c r="D591" t="s">
-        <v>529</v>
+        <v>509</v>
       </c>
       <c r="E591" t="s">
         <v>65</v>
@@ -13090,7 +13077,7 @@
         <v>35</v>
       </c>
       <c r="D592" t="s">
-        <v>530</v>
+        <v>510</v>
       </c>
       <c r="E592" t="s">
         <v>65</v>
@@ -13105,7 +13092,7 @@
         <v>35</v>
       </c>
       <c r="D593" t="s">
-        <v>531</v>
+        <v>511</v>
       </c>
       <c r="E593" t="s">
         <v>65</v>
@@ -13120,7 +13107,7 @@
         <v>35</v>
       </c>
       <c r="D594" t="s">
-        <v>532</v>
+        <v>512</v>
       </c>
       <c r="E594" t="s">
         <v>65</v>
@@ -13135,7 +13122,7 @@
         <v>35</v>
       </c>
       <c r="D595" t="s">
-        <v>533</v>
+        <v>513</v>
       </c>
       <c r="E595" t="s">
         <v>65</v>
@@ -13150,7 +13137,7 @@
         <v>35</v>
       </c>
       <c r="D596" t="s">
-        <v>534</v>
+        <v>514</v>
       </c>
       <c r="E596" t="s">
         <v>65</v>
@@ -13225,7 +13212,7 @@
         <v>36</v>
       </c>
       <c r="B601" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="D601" t="s">
         <v>84</v>
@@ -13243,7 +13230,7 @@
         <v>36</v>
       </c>
       <c r="B602" t="s">
-        <v>535</v>
+        <v>515</v>
       </c>
       <c r="D602" t="s">
         <v>85</v>
@@ -13261,7 +13248,7 @@
         <v>36</v>
       </c>
       <c r="B603" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="D603" t="s">
         <v>84</v>
@@ -13279,10 +13266,10 @@
         <v>36</v>
       </c>
       <c r="B604" t="s">
-        <v>536</v>
+        <v>516</v>
       </c>
       <c r="D604" t="s">
-        <v>537</v>
+        <v>517</v>
       </c>
       <c r="E604" t="s">
         <v>65</v>
@@ -13297,10 +13284,10 @@
         <v>36</v>
       </c>
       <c r="B605" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="D605" t="s">
-        <v>539</v>
+        <v>519</v>
       </c>
       <c r="E605" t="s">
         <v>65</v>
@@ -13315,10 +13302,10 @@
         <v>36</v>
       </c>
       <c r="B606" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="D606" t="s">
-        <v>540</v>
+        <v>520</v>
       </c>
       <c r="E606" t="s">
         <v>65</v>
@@ -13333,10 +13320,10 @@
         <v>36</v>
       </c>
       <c r="B607" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="D607" t="s">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="E607" t="s">
         <v>65</v>
@@ -13351,7 +13338,7 @@
         <v>36</v>
       </c>
       <c r="B608" t="s">
-        <v>538</v>
+        <v>518</v>
       </c>
       <c r="D608" t="s">
         <v>71</v>
@@ -13369,10 +13356,10 @@
         <v>37</v>
       </c>
       <c r="B609" t="s">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="D609" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="E609" t="s">
         <v>65</v>
@@ -13387,10 +13374,10 @@
         <v>37</v>
       </c>
       <c r="B610" t="s">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="D610" t="s">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="E610" t="s">
         <v>65</v>
@@ -13405,7 +13392,7 @@
         <v>37</v>
       </c>
       <c r="B611" t="s">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="D611" t="s">
         <v>67</v>
@@ -13423,10 +13410,10 @@
         <v>37</v>
       </c>
       <c r="B612" t="s">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="D612" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="E612" t="s">
         <v>65</v>
@@ -13441,10 +13428,10 @@
         <v>37</v>
       </c>
       <c r="B613" t="s">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="D613" t="s">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="E613" t="s">
         <v>65</v>
@@ -13459,7 +13446,7 @@
         <v>37</v>
       </c>
       <c r="B614" t="s">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="D614" t="s">
         <v>67</v>
@@ -13477,7 +13464,7 @@
         <v>37</v>
       </c>
       <c r="B615" t="s">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="D615" t="s">
         <v>106</v>
@@ -13495,7 +13482,7 @@
         <v>37</v>
       </c>
       <c r="B616" t="s">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="D616" t="s">
         <v>67</v>
@@ -13513,7 +13500,7 @@
         <v>37</v>
       </c>
       <c r="B617" t="s">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="D617" t="s">
         <v>106</v>
@@ -13531,10 +13518,10 @@
         <v>37</v>
       </c>
       <c r="B618" t="s">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="D618" t="s">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="E618" t="s">
         <v>46</v>
@@ -13549,7 +13536,7 @@
         <v>38</v>
       </c>
       <c r="D619" t="s">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="E619" t="s">
         <v>46</v>
@@ -13564,7 +13551,7 @@
         <v>38</v>
       </c>
       <c r="D620" t="s">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="E620" t="s">
         <v>46</v>
@@ -13579,7 +13566,7 @@
         <v>38</v>
       </c>
       <c r="D621" t="s">
-        <v>551</v>
+        <v>531</v>
       </c>
       <c r="E621" t="s">
         <v>46</v>
@@ -13594,7 +13581,7 @@
         <v>38</v>
       </c>
       <c r="D622" t="s">
-        <v>552</v>
+        <v>532</v>
       </c>
       <c r="E622" t="s">
         <v>46</v>
@@ -13602,66 +13589,6 @@
       <c r="F622" t="str">
         <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
         <v>f0621</v>
-      </c>
-    </row>
-    <row r="623" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F623" t="str">
-        <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
-        <v>f0622</v>
-      </c>
-    </row>
-    <row r="624" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="F624" t="str">
-        <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
-        <v>f0623</v>
-      </c>
-    </row>
-    <row r="625" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F625" t="str">
-        <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
-        <v>f0624</v>
-      </c>
-    </row>
-    <row r="626" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F626" t="str">
-        <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
-        <v>f0625</v>
-      </c>
-    </row>
-    <row r="627" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F627" t="str">
-        <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
-        <v>f0626</v>
-      </c>
-    </row>
-    <row r="628" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F628" t="str">
-        <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
-        <v>f0627</v>
-      </c>
-    </row>
-    <row r="629" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F629" t="str">
-        <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
-        <v>f0628</v>
-      </c>
-    </row>
-    <row r="630" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F630" t="str">
-        <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
-        <v>f0629</v>
-      </c>
-    </row>
-    <row r="631" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F631" t="str">
-        <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
-        <v>f0630</v>
-      </c>
-    </row>
-    <row r="632" spans="6:6" x14ac:dyDescent="0.35">
-      <c r="F632" t="str">
-        <f>"f" &amp; TEXT(ROW()-ROW(Table1[[#Headers],[Placeholder]]), "0000")</f>
-        <v>f0631</v>
       </c>
     </row>
   </sheetData>
